--- a/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY92"/>
+  <dimension ref="A1:AY99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,45 +1347,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135333195</v>
+        <v>135337856</v>
       </c>
       <c r="B8" t="n">
-        <v>91974</v>
+        <v>92795</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>918</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623422</v>
+        <v>623566</v>
       </c>
       <c r="R8" t="n">
-        <v>7307495</v>
+        <v>7307479</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1427,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran rörligt markvatten. Har kollekt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,18 +1441,19 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1458,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135331141</v>
+        <v>135333195</v>
       </c>
       <c r="B9" t="n">
-        <v>83222</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,34 +1475,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623557</v>
+        <v>623422</v>
       </c>
       <c r="R9" t="n">
-        <v>7307476</v>
+        <v>7307495</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1528,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1538,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,12 +1559,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1569,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135331135</v>
+        <v>135331141</v>
       </c>
       <c r="B10" t="n">
-        <v>92167</v>
+        <v>83222</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1580,21 +1586,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1588</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1604,13 +1610,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623561</v>
+        <v>623557</v>
       </c>
       <c r="R10" t="n">
-        <v>7307325</v>
+        <v>7307476</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1639,7 +1645,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1649,7 +1655,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1680,7 +1686,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135331140</v>
+        <v>135331135</v>
       </c>
       <c r="B11" t="n">
         <v>92167</v>
@@ -1715,13 +1721,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623575</v>
+        <v>623561</v>
       </c>
       <c r="R11" t="n">
-        <v>7307427</v>
+        <v>7307325</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1750,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1760,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1791,32 +1797,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135331131</v>
+        <v>135331140</v>
       </c>
       <c r="B12" t="n">
-        <v>96678</v>
+        <v>92167</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2166</v>
+        <v>1588</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1826,13 +1832,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623557</v>
+        <v>623575</v>
       </c>
       <c r="R12" t="n">
-        <v>7307301</v>
+        <v>7307427</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1861,7 +1867,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1871,7 +1877,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135331132</v>
+        <v>135331131</v>
       </c>
       <c r="B13" t="n">
-        <v>97308</v>
+        <v>96678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,21 +1919,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2869</v>
+        <v>2166</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,13 +1943,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623545</v>
+        <v>623557</v>
       </c>
       <c r="R13" t="n">
-        <v>7307305</v>
+        <v>7307301</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2013,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135320627</v>
+        <v>135331132</v>
       </c>
       <c r="B14" t="n">
-        <v>91937</v>
+        <v>97308</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,37 +2030,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623517</v>
+        <v>623545</v>
       </c>
       <c r="R14" t="n">
-        <v>7307459</v>
+        <v>7307305</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2083,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2093,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,44 +2114,48 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135319473</v>
+        <v>135320627</v>
       </c>
       <c r="B15" t="n">
-        <v>79373</v>
+        <v>91937</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2165,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623472</v>
+        <v>623517</v>
       </c>
       <c r="R15" t="n">
-        <v>7307510</v>
+        <v>7307459</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2190,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2200,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2227,7 +2237,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135319562</v>
+        <v>135319473</v>
       </c>
       <c r="B16" t="n">
         <v>79373</v>
@@ -2262,10 +2272,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623499</v>
+        <v>623472</v>
       </c>
       <c r="R16" t="n">
-        <v>7307488</v>
+        <v>7307510</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2297,7 +2307,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2307,7 +2317,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2334,7 +2344,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135333184</v>
+        <v>135319562</v>
       </c>
       <c r="B17" t="n">
         <v>79373</v>
@@ -2365,17 +2375,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623581</v>
+        <v>623499</v>
       </c>
       <c r="R17" t="n">
-        <v>7307301</v>
+        <v>7307488</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2404,7 +2414,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2414,7 +2424,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2429,23 +2439,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135333188</v>
+        <v>135333184</v>
       </c>
       <c r="B18" t="n">
         <v>79373</v>
@@ -2480,13 +2486,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623541</v>
+        <v>623581</v>
       </c>
       <c r="R18" t="n">
-        <v>7307359</v>
+        <v>7307301</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2515,7 +2521,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2525,7 +2531,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2556,7 +2562,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135333190</v>
+        <v>135333188</v>
       </c>
       <c r="B19" t="n">
         <v>79373</v>
@@ -2591,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623521</v>
+        <v>623541</v>
       </c>
       <c r="R19" t="n">
-        <v>7307382</v>
+        <v>7307359</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2626,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2636,7 +2642,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2667,48 +2673,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135320009</v>
+        <v>135333190</v>
       </c>
       <c r="B20" t="n">
-        <v>78776</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623461</v>
+        <v>623521</v>
       </c>
       <c r="R20" t="n">
-        <v>7307589</v>
+        <v>7307382</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2737,7 +2743,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2747,7 +2753,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2762,22 +2768,26 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135333183</v>
+        <v>135320009</v>
       </c>
       <c r="B21" t="n">
-        <v>83358</v>
+        <v>78776</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2785,37 +2795,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623578</v>
+        <v>623461</v>
       </c>
       <c r="R21" t="n">
-        <v>7307305</v>
+        <v>7307589</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2844,7 +2854,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2854,7 +2864,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2869,26 +2879,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135319971</v>
+        <v>135333183</v>
       </c>
       <c r="B22" t="n">
-        <v>79992</v>
+        <v>83358</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2896,37 +2902,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623461</v>
+        <v>623578</v>
       </c>
       <c r="R22" t="n">
-        <v>7307589</v>
+        <v>7307305</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2955,7 +2961,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2965,7 +2971,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2980,19 +2986,23 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135333185</v>
+        <v>135319971</v>
       </c>
       <c r="B23" t="n">
         <v>79992</v>
@@ -3023,17 +3033,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>623521</v>
+        <v>623461</v>
       </c>
       <c r="R23" t="n">
-        <v>7307328</v>
+        <v>7307589</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3062,7 +3072,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3072,7 +3082,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3087,48 +3097,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135333191</v>
+        <v>135333185</v>
       </c>
       <c r="B24" t="n">
-        <v>80500</v>
+        <v>79992</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3138,13 +3144,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623500</v>
+        <v>623521</v>
       </c>
       <c r="R24" t="n">
-        <v>7307377</v>
+        <v>7307328</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3173,7 +3179,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3183,7 +3189,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3214,48 +3220,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135319479</v>
+        <v>135333191</v>
       </c>
       <c r="B25" t="n">
-        <v>57975</v>
+        <v>80500</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>623472</v>
+        <v>623500</v>
       </c>
       <c r="R25" t="n">
-        <v>7307510</v>
+        <v>7307377</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3284,7 +3290,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3294,12 +3300,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Spår</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3314,19 +3315,23 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135319812</v>
+        <v>135319479</v>
       </c>
       <c r="B26" t="n">
         <v>57975</v>
@@ -3361,10 +3366,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>623492</v>
+        <v>623472</v>
       </c>
       <c r="R26" t="n">
-        <v>7307534</v>
+        <v>7307510</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3396,7 +3401,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3406,7 +3411,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3438,7 +3443,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135320195</v>
+        <v>135319812</v>
       </c>
       <c r="B27" t="n">
         <v>57975</v>
@@ -3473,10 +3478,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>623500</v>
+        <v>623492</v>
       </c>
       <c r="R27" t="n">
-        <v>7307689</v>
+        <v>7307534</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3508,7 +3513,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3518,7 +3523,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3550,7 +3555,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135320511</v>
+        <v>135320195</v>
       </c>
       <c r="B28" t="n">
         <v>57975</v>
@@ -3585,10 +3590,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>623489</v>
+        <v>623500</v>
       </c>
       <c r="R28" t="n">
-        <v>7307496</v>
+        <v>7307689</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3620,7 +3625,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3630,12 +3635,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Gamla spår</t>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3662,32 +3667,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135319835</v>
+        <v>135320511</v>
       </c>
       <c r="B29" t="n">
-        <v>98060</v>
+        <v>57975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3697,10 +3702,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>623492</v>
+        <v>623489</v>
       </c>
       <c r="R29" t="n">
-        <v>7307534</v>
+        <v>7307496</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3732,7 +3737,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3742,7 +3747,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Gamla spår</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3769,10 +3779,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135331126</v>
+        <v>135337854</v>
       </c>
       <c r="B30" t="n">
-        <v>79963</v>
+        <v>57975</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3780,37 +3790,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>623584</v>
+        <v>623570</v>
       </c>
       <c r="R30" t="n">
-        <v>7307249</v>
+        <v>7307448</v>
       </c>
       <c r="S30" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3839,7 +3849,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3849,7 +3859,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3864,12 +3879,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3880,10 +3895,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135331128</v>
+        <v>135337855</v>
       </c>
       <c r="B31" t="n">
-        <v>79963</v>
+        <v>57975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3891,37 +3906,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>623566</v>
+        <v>623573</v>
       </c>
       <c r="R31" t="n">
-        <v>7307255</v>
+        <v>7307467</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3950,7 +3965,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3960,7 +3975,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3975,12 +3995,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3991,10 +4011,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135333186</v>
+        <v>135337857</v>
       </c>
       <c r="B32" t="n">
-        <v>79963</v>
+        <v>57975</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4002,37 +4022,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>623526</v>
+        <v>623573</v>
       </c>
       <c r="R32" t="n">
-        <v>7307330</v>
+        <v>7307487</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4061,7 +4085,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4071,7 +4095,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Spår på två träd</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4086,12 +4115,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4102,48 +4131,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135331143</v>
+        <v>135337862</v>
       </c>
       <c r="B33" t="n">
-        <v>83350</v>
+        <v>106309</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>221725</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>623620</v>
+        <v>623573</v>
       </c>
       <c r="R33" t="n">
-        <v>7307390</v>
+        <v>7307459</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4167,22 +4196,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4197,12 +4226,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4213,48 +4242,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135331036</v>
+        <v>135319835</v>
       </c>
       <c r="B34" t="n">
-        <v>79039</v>
+        <v>98060</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>623619</v>
+        <v>623492</v>
       </c>
       <c r="R34" t="n">
-        <v>7307249</v>
+        <v>7307534</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4281,9 +4310,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4298,26 +4337,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135332782</v>
+        <v>135331126</v>
       </c>
       <c r="B35" t="n">
-        <v>79039</v>
+        <v>79963</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4325,37 +4360,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>623828</v>
+        <v>623584</v>
       </c>
       <c r="R35" t="n">
-        <v>7307383</v>
+        <v>7307249</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4384,7 +4419,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4394,7 +4429,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4409,12 +4444,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4425,32 +4460,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135331144</v>
+        <v>135331128</v>
       </c>
       <c r="B36" t="n">
-        <v>83349</v>
+        <v>79963</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>492</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4460,13 +4495,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>623602</v>
+        <v>623566</v>
       </c>
       <c r="R36" t="n">
-        <v>7307395</v>
+        <v>7307255</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4495,7 +4530,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4505,7 +4540,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4514,7 +4549,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4537,10 +4571,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135333369</v>
+        <v>135333186</v>
       </c>
       <c r="B37" t="n">
-        <v>79452</v>
+        <v>79963</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4548,34 +4582,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>864</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>624013</v>
+        <v>623526</v>
       </c>
       <c r="R37" t="n">
-        <v>7307360</v>
+        <v>7307330</v>
       </c>
       <c r="S37" t="n">
         <v>6</v>
@@ -4607,7 +4641,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4617,7 +4651,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4632,12 +4666,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4648,48 +4682,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135333379</v>
+        <v>135331143</v>
       </c>
       <c r="B38" t="n">
-        <v>92795</v>
+        <v>83350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>918</v>
+        <v>308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>624069</v>
+        <v>623620</v>
       </c>
       <c r="R38" t="n">
-        <v>7307333</v>
+        <v>7307390</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4718,7 +4752,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4728,7 +4762,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4743,12 +4777,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4759,10 +4793,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135331034</v>
+        <v>135331036</v>
       </c>
       <c r="B39" t="n">
-        <v>81355</v>
+        <v>79039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4770,21 +4804,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4794,13 +4828,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>623627</v>
+        <v>623619</v>
       </c>
       <c r="R39" t="n">
-        <v>7307253</v>
+        <v>7307249</v>
       </c>
       <c r="S39" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4860,10 +4894,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135331031</v>
+        <v>135332782</v>
       </c>
       <c r="B40" t="n">
-        <v>91970</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4871,34 +4905,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>623666</v>
+        <v>623828</v>
       </c>
       <c r="R40" t="n">
-        <v>7307292</v>
+        <v>7307383</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4928,9 +4962,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4945,12 +4989,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4961,48 +5005,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135331028</v>
+        <v>135331144</v>
       </c>
       <c r="B41" t="n">
-        <v>83222</v>
+        <v>83349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>492</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>623662</v>
+        <v>623602</v>
       </c>
       <c r="R41" t="n">
-        <v>7307297</v>
+        <v>7307395</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5029,29 +5073,40 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5062,10 +5117,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135331037</v>
+        <v>135333369</v>
       </c>
       <c r="B42" t="n">
-        <v>83222</v>
+        <v>79452</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5073,37 +5128,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>623600</v>
+        <v>624013</v>
       </c>
       <c r="R42" t="n">
-        <v>7307269</v>
+        <v>7307360</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5130,9 +5185,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5147,12 +5212,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5163,32 +5228,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135332774</v>
+        <v>135333379</v>
       </c>
       <c r="B43" t="n">
-        <v>83222</v>
+        <v>92795</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>918</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5198,13 +5263,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>623973</v>
+        <v>624069</v>
       </c>
       <c r="R43" t="n">
-        <v>7307330</v>
+        <v>7307333</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5233,7 +5298,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5243,7 +5308,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5258,12 +5323,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5274,10 +5339,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135333363</v>
+        <v>135331034</v>
       </c>
       <c r="B44" t="n">
-        <v>83222</v>
+        <v>81355</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5285,37 +5350,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>1049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>624035</v>
+        <v>623627</v>
       </c>
       <c r="R44" t="n">
-        <v>7307280</v>
+        <v>7307253</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5342,19 +5407,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5369,12 +5424,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5385,10 +5440,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135333367</v>
+        <v>135331031</v>
       </c>
       <c r="B45" t="n">
-        <v>83222</v>
+        <v>91970</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5396,37 +5451,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>624036</v>
+        <v>623666</v>
       </c>
       <c r="R45" t="n">
-        <v>7307333</v>
+        <v>7307292</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5453,19 +5508,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5480,12 +5525,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5496,10 +5541,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135333370</v>
+        <v>135337861</v>
       </c>
       <c r="B46" t="n">
-        <v>83222</v>
+        <v>91974</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5507,34 +5552,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>624014</v>
+        <v>623609</v>
       </c>
       <c r="R46" t="n">
-        <v>7307360</v>
+        <v>7307443</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5566,7 +5611,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5576,7 +5621,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På tall över fuktigt vatten</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5585,18 +5635,19 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5607,7 +5658,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135333377</v>
+        <v>135331028</v>
       </c>
       <c r="B47" t="n">
         <v>83222</v>
@@ -5638,17 +5689,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>623784</v>
+        <v>623662</v>
       </c>
       <c r="R47" t="n">
-        <v>7307352</v>
+        <v>7307297</v>
       </c>
       <c r="S47" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5675,19 +5726,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>16:34</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>16:34</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5702,12 +5743,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5718,10 +5759,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135331123</v>
+        <v>135331037</v>
       </c>
       <c r="B48" t="n">
-        <v>91896</v>
+        <v>83222</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5729,37 +5770,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3242</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>623681</v>
+        <v>623600</v>
       </c>
       <c r="R48" t="n">
-        <v>7307293</v>
+        <v>7307269</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5786,19 +5827,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>14:26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5813,12 +5844,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5829,32 +5860,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135332769</v>
+        <v>135332774</v>
       </c>
       <c r="B49" t="n">
-        <v>91937</v>
+        <v>83222</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5864,13 +5895,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>624069</v>
+        <v>623973</v>
       </c>
       <c r="R49" t="n">
-        <v>7307267</v>
+        <v>7307330</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5899,7 +5930,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5909,7 +5940,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5940,48 +5971,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135331027</v>
+        <v>135333363</v>
       </c>
       <c r="B50" t="n">
-        <v>79373</v>
+        <v>83222</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>623680</v>
+        <v>624035</v>
       </c>
       <c r="R50" t="n">
-        <v>7307293</v>
+        <v>7307280</v>
       </c>
       <c r="S50" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6008,9 +6039,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6025,12 +6066,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6041,48 +6082,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135331029</v>
+        <v>135333367</v>
       </c>
       <c r="B51" t="n">
-        <v>79373</v>
+        <v>83222</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>623660</v>
+        <v>624036</v>
       </c>
       <c r="R51" t="n">
-        <v>7307297</v>
+        <v>7307333</v>
       </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6109,9 +6150,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6126,12 +6177,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6142,48 +6193,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135331670</v>
+        <v>135333370</v>
       </c>
       <c r="B52" t="n">
-        <v>79373</v>
+        <v>83222</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>624012</v>
+        <v>624014</v>
       </c>
       <c r="R52" t="n">
-        <v>7307326</v>
+        <v>7307360</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6212,7 +6263,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6222,7 +6273,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6237,12 +6288,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6253,10 +6304,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135331033</v>
+        <v>135333377</v>
       </c>
       <c r="B53" t="n">
-        <v>78776</v>
+        <v>83222</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6264,37 +6315,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>623649</v>
+        <v>623784</v>
       </c>
       <c r="R53" t="n">
-        <v>7307278</v>
+        <v>7307352</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6321,9 +6372,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6338,12 +6399,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6354,10 +6415,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135333364</v>
+        <v>135331123</v>
       </c>
       <c r="B54" t="n">
-        <v>78776</v>
+        <v>91896</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6365,37 +6426,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6437</v>
+        <v>3242</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>624037</v>
+        <v>623681</v>
       </c>
       <c r="R54" t="n">
-        <v>7307285</v>
+        <v>7307293</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6424,7 +6485,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6434,7 +6495,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6449,12 +6510,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6465,32 +6526,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135333375</v>
+        <v>135332769</v>
       </c>
       <c r="B55" t="n">
-        <v>78776</v>
+        <v>91937</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6500,10 +6561,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>623832</v>
+        <v>624069</v>
       </c>
       <c r="R55" t="n">
-        <v>7307315</v>
+        <v>7307267</v>
       </c>
       <c r="S55" t="n">
         <v>6</v>
@@ -6535,7 +6596,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6545,7 +6606,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6560,12 +6621,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6576,48 +6637,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135332772</v>
+        <v>135331027</v>
       </c>
       <c r="B56" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>624017</v>
+        <v>623680</v>
       </c>
       <c r="R56" t="n">
-        <v>7307324</v>
+        <v>7307293</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6644,19 +6705,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:49</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6671,12 +6722,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6687,48 +6738,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135332775</v>
+        <v>135331029</v>
       </c>
       <c r="B57" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>623971</v>
+        <v>623660</v>
       </c>
       <c r="R57" t="n">
-        <v>7307331</v>
+        <v>7307297</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6755,19 +6806,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>16:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6782,12 +6823,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6798,48 +6839,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135331035</v>
+        <v>135331670</v>
       </c>
       <c r="B58" t="n">
-        <v>79992</v>
+        <v>79373</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>623629</v>
+        <v>624012</v>
       </c>
       <c r="R58" t="n">
-        <v>7307251</v>
+        <v>7307326</v>
       </c>
       <c r="S58" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6866,9 +6907,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6883,12 +6934,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6899,10 +6950,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135332771</v>
+        <v>135331033</v>
       </c>
       <c r="B59" t="n">
-        <v>79992</v>
+        <v>78776</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6910,37 +6961,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>624036</v>
+        <v>623649</v>
       </c>
       <c r="R59" t="n">
-        <v>7307307</v>
+        <v>7307278</v>
       </c>
       <c r="S59" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6967,19 +7018,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>15:44</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6994,12 +7035,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7010,10 +7051,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135332776</v>
+        <v>135333364</v>
       </c>
       <c r="B60" t="n">
-        <v>79992</v>
+        <v>78776</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7021,21 +7062,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7045,13 +7086,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>623926</v>
+        <v>624037</v>
       </c>
       <c r="R60" t="n">
-        <v>7307301</v>
+        <v>7307285</v>
       </c>
       <c r="S60" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7080,7 +7121,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7090,7 +7131,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7105,12 +7146,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7121,10 +7162,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135333181</v>
+        <v>135333375</v>
       </c>
       <c r="B61" t="n">
-        <v>79992</v>
+        <v>78776</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7132,37 +7173,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>623638</v>
+        <v>623832</v>
       </c>
       <c r="R61" t="n">
-        <v>7307259</v>
+        <v>7307315</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7191,7 +7232,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7201,7 +7242,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7216,12 +7257,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7232,32 +7273,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135333371</v>
+        <v>135332772</v>
       </c>
       <c r="B62" t="n">
-        <v>57972</v>
+        <v>83358</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7267,13 +7308,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>624014</v>
+        <v>624017</v>
       </c>
       <c r="R62" t="n">
-        <v>7307360</v>
+        <v>7307324</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7302,7 +7343,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7312,7 +7353,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7327,12 +7368,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7343,32 +7384,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135333374</v>
+        <v>135332775</v>
       </c>
       <c r="B63" t="n">
-        <v>57972</v>
+        <v>83358</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7378,10 +7419,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>623919</v>
+        <v>623971</v>
       </c>
       <c r="R63" t="n">
-        <v>7307361</v>
+        <v>7307331</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7413,7 +7454,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7423,12 +7464,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7443,12 +7479,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7459,10 +7495,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135318090</v>
+        <v>135331035</v>
       </c>
       <c r="B64" t="n">
-        <v>57975</v>
+        <v>79992</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7470,37 +7506,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>623800</v>
+        <v>623629</v>
       </c>
       <c r="R64" t="n">
-        <v>7307412</v>
+        <v>7307251</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7527,19 +7563,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7554,22 +7580,26 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135331038</v>
+        <v>135332771</v>
       </c>
       <c r="B65" t="n">
-        <v>57975</v>
+        <v>79992</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7577,37 +7607,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>623589</v>
+        <v>624036</v>
       </c>
       <c r="R65" t="n">
-        <v>7307264</v>
+        <v>7307307</v>
       </c>
       <c r="S65" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7634,14 +7664,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7656,12 +7691,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7672,10 +7707,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135332777</v>
+        <v>135332776</v>
       </c>
       <c r="B66" t="n">
-        <v>57975</v>
+        <v>79992</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7683,42 +7718,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>623904</v>
+        <v>623926</v>
       </c>
       <c r="R66" t="n">
-        <v>7307334</v>
+        <v>7307301</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7747,7 +7777,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7757,7 +7787,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7788,10 +7818,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135332781</v>
+        <v>135333181</v>
       </c>
       <c r="B67" t="n">
-        <v>57975</v>
+        <v>79992</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7799,42 +7829,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>623790</v>
+        <v>623638</v>
       </c>
       <c r="R67" t="n">
-        <v>7307346</v>
+        <v>7307259</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7863,7 +7888,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7873,7 +7898,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7888,12 +7913,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7904,27 +7929,27 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135332783</v>
+        <v>135333371</v>
       </c>
       <c r="B68" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7939,13 +7964,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>623971</v>
+        <v>624014</v>
       </c>
       <c r="R68" t="n">
-        <v>7307384</v>
+        <v>7307360</v>
       </c>
       <c r="S68" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7974,7 +7999,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7984,19 +8009,14 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>skalade undertryckta granar, flera stycken</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="b">
         <v>0</v>
@@ -8004,12 +8024,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8020,27 +8040,27 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135332786</v>
+        <v>135333374</v>
       </c>
       <c r="B69" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8049,24 +8069,19 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>624077</v>
+        <v>623919</v>
       </c>
       <c r="R69" t="n">
-        <v>7307313</v>
+        <v>7307361</v>
       </c>
       <c r="S69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8095,7 +8110,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8105,7 +8120,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8120,12 +8140,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8136,7 +8156,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135333182</v>
+        <v>135318090</v>
       </c>
       <c r="B70" t="n">
         <v>57975</v>
@@ -8167,17 +8187,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>623602</v>
+        <v>623800</v>
       </c>
       <c r="R70" t="n">
-        <v>7307284</v>
+        <v>7307412</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8206,7 +8226,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8216,12 +8236,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8236,64 +8251,60 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135331121</v>
+        <v>135331038</v>
       </c>
       <c r="B71" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>623943</v>
+        <v>623589</v>
       </c>
       <c r="R71" t="n">
-        <v>7307296</v>
+        <v>7307264</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8320,19 +8331,14 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>14:12</t>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8347,12 +8353,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8363,45 +8369,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135331122</v>
+        <v>135332777</v>
       </c>
       <c r="B72" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>623926</v>
+        <v>623904</v>
       </c>
       <c r="R72" t="n">
-        <v>7307337</v>
+        <v>7307334</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8433,7 +8444,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8443,12 +8454,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Tjäderbo? eller uppehallsplats?</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8463,12 +8469,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8479,48 +8485,53 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135331032</v>
+        <v>135332781</v>
       </c>
       <c r="B73" t="n">
-        <v>5181</v>
+        <v>57975</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>623649</v>
+        <v>623790</v>
       </c>
       <c r="R73" t="n">
-        <v>7307278</v>
+        <v>7307346</v>
       </c>
       <c r="S73" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8547,14 +8558,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Gnag</t>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8569,12 +8585,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8585,32 +8601,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135333376</v>
+        <v>135332783</v>
       </c>
       <c r="B74" t="n">
-        <v>5181</v>
+        <v>57975</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8620,13 +8636,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>623799</v>
+        <v>623971</v>
       </c>
       <c r="R74" t="n">
-        <v>7307327</v>
+        <v>7307384</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8655,7 +8671,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8665,19 +8681,19 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Gnag</t>
+          <t>skalade undertryckta granar, flera stycken</t>
         </is>
       </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG74" t="b">
         <v>0</v>
@@ -8685,12 +8701,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8701,10 +8717,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135332770</v>
+        <v>135332786</v>
       </c>
       <c r="B75" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8712,37 +8728,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>624031</v>
+        <v>624077</v>
       </c>
       <c r="R75" t="n">
-        <v>7307306</v>
+        <v>7307313</v>
       </c>
       <c r="S75" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8771,7 +8792,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8781,7 +8802,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8812,10 +8833,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135333365</v>
+        <v>135333182</v>
       </c>
       <c r="B76" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8823,37 +8844,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>624039</v>
+        <v>623602</v>
       </c>
       <c r="R76" t="n">
-        <v>7307316</v>
+        <v>7307284</v>
       </c>
       <c r="S76" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8882,7 +8903,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8892,7 +8913,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8907,12 +8933,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8923,10 +8949,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135333378</v>
+        <v>135337852</v>
       </c>
       <c r="B77" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8934,37 +8960,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>624079</v>
+        <v>623747</v>
       </c>
       <c r="R77" t="n">
-        <v>7307360</v>
+        <v>7307427</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8993,7 +9019,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9003,12 +9029,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Familjegrupp, minst 5 st</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9023,12 +9049,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9039,10 +9065,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135331030</v>
+        <v>135331121</v>
       </c>
       <c r="B78" t="n">
-        <v>5201</v>
+        <v>57162</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9050,37 +9076,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>623665</v>
+        <v>623943</v>
       </c>
       <c r="R78" t="n">
-        <v>7307294</v>
+        <v>7307296</v>
       </c>
       <c r="S78" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9107,14 +9133,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Gnag</t>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9129,12 +9160,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9145,10 +9176,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135333372</v>
+        <v>135331122</v>
       </c>
       <c r="B79" t="n">
-        <v>99099</v>
+        <v>57162</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9156,34 +9187,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220093</v>
+        <v>100138</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>624008</v>
+        <v>623926</v>
       </c>
       <c r="R79" t="n">
-        <v>7307352</v>
+        <v>7307337</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9215,7 +9246,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9225,12 +9256,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Kolla</t>
+          <t>Tjäderbo? eller uppehallsplats?</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9245,12 +9276,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9261,10 +9292,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135331671</v>
+        <v>135331032</v>
       </c>
       <c r="B80" t="n">
-        <v>98060</v>
+        <v>5181</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9272,37 +9303,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>623997</v>
+        <v>623649</v>
       </c>
       <c r="R80" t="n">
-        <v>7307348</v>
+        <v>7307278</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9329,19 +9360,14 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>15:57</t>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9356,12 +9382,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9372,10 +9398,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135331145</v>
+        <v>135333376</v>
       </c>
       <c r="B81" t="n">
-        <v>99217</v>
+        <v>5181</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9383,37 +9409,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221952</v>
+        <v>100526</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>623644</v>
+        <v>623799</v>
       </c>
       <c r="R81" t="n">
-        <v>7307354</v>
+        <v>7307327</v>
       </c>
       <c r="S81" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9442,7 +9468,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9452,7 +9478,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9467,12 +9498,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9483,48 +9514,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135331672</v>
+        <v>135332770</v>
       </c>
       <c r="B82" t="n">
-        <v>99217</v>
+        <v>58136</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>624001</v>
+        <v>624031</v>
       </c>
       <c r="R82" t="n">
-        <v>7307352</v>
+        <v>7307306</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9553,7 +9584,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9563,7 +9594,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9578,12 +9609,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9594,48 +9625,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135331673</v>
+        <v>135333365</v>
       </c>
       <c r="B83" t="n">
-        <v>99217</v>
+        <v>58136</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>623969</v>
+        <v>624039</v>
       </c>
       <c r="R83" t="n">
-        <v>7307338</v>
+        <v>7307316</v>
       </c>
       <c r="S83" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9664,7 +9695,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9674,7 +9705,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9689,12 +9720,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9705,48 +9736,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135331674</v>
+        <v>135333378</v>
       </c>
       <c r="B84" t="n">
-        <v>99217</v>
+        <v>58136</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>623948</v>
+        <v>624079</v>
       </c>
       <c r="R84" t="n">
-        <v>7307327</v>
+        <v>7307360</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9775,7 +9806,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9785,7 +9816,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Familjegrupp, minst 5 st</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9800,12 +9836,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9816,32 +9852,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135331039</v>
+        <v>135331030</v>
       </c>
       <c r="B85" t="n">
-        <v>79963</v>
+        <v>5201</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229821</v>
+        <v>105930</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9851,13 +9887,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>623714</v>
+        <v>623665</v>
       </c>
       <c r="R85" t="n">
-        <v>7307148</v>
+        <v>7307294</v>
       </c>
       <c r="S85" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9887,6 +9923,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9917,45 +9958,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135331124</v>
+        <v>135333372</v>
       </c>
       <c r="B86" t="n">
-        <v>79963</v>
+        <v>99099</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229821</v>
+        <v>220093</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>623675</v>
+        <v>624008</v>
       </c>
       <c r="R86" t="n">
-        <v>7307271</v>
+        <v>7307352</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9987,7 +10028,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9997,7 +10038,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Kolla</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10012,12 +10058,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -10028,48 +10074,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135331125</v>
+        <v>135331671</v>
       </c>
       <c r="B87" t="n">
-        <v>79963</v>
+        <v>98060</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>623635</v>
+        <v>623997</v>
       </c>
       <c r="R87" t="n">
-        <v>7307226</v>
+        <v>7307348</v>
       </c>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10098,7 +10144,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10108,12 +10154,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Stubbe med yxhugg ser bild</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10128,12 +10169,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10144,32 +10185,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135331119</v>
+        <v>135331145</v>
       </c>
       <c r="B88" t="n">
-        <v>79396</v>
+        <v>99217</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>260591</v>
+        <v>221952</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10179,13 +10220,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>624074</v>
+        <v>623644</v>
       </c>
       <c r="R88" t="n">
-        <v>7307283</v>
+        <v>7307354</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10214,7 +10255,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10224,7 +10265,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10233,7 +10274,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -10256,32 +10296,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135331669</v>
+        <v>135331672</v>
       </c>
       <c r="B89" t="n">
-        <v>79396</v>
+        <v>99217</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>260591</v>
+        <v>221952</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10291,13 +10331,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>624037</v>
+        <v>624001</v>
       </c>
       <c r="R89" t="n">
-        <v>7307291</v>
+        <v>7307352</v>
       </c>
       <c r="S89" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10326,7 +10366,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10336,7 +10376,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10367,48 +10407,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135332778</v>
+        <v>135331673</v>
       </c>
       <c r="B90" t="n">
-        <v>79396</v>
+        <v>99217</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>260591</v>
+        <v>221952</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>623849</v>
+        <v>623969</v>
       </c>
       <c r="R90" t="n">
-        <v>7307318</v>
+        <v>7307338</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10437,7 +10477,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10447,7 +10487,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10462,12 +10502,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -10478,48 +10518,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135333180</v>
+        <v>135331674</v>
       </c>
       <c r="B91" t="n">
-        <v>79396</v>
+        <v>99217</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>260591</v>
+        <v>221952</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>623673</v>
+        <v>623948</v>
       </c>
       <c r="R91" t="n">
-        <v>7307275</v>
+        <v>7307327</v>
       </c>
       <c r="S91" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10548,7 +10588,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10558,7 +10598,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10573,12 +10613,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10589,10 +10629,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135333382</v>
+        <v>135331039</v>
       </c>
       <c r="B92" t="n">
-        <v>79396</v>
+        <v>79963</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10600,37 +10640,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>624084</v>
+        <v>623714</v>
       </c>
       <c r="R92" t="n">
-        <v>7307323</v>
+        <v>7307148</v>
       </c>
       <c r="S92" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10657,19 +10697,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>16:50</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10684,15 +10714,798 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>135331124</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>623675</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7307271</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>135331125</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>623635</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7307226</v>
+      </c>
+      <c r="S94" t="n">
+        <v>9</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Stubbe med yxhugg ser bild</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>135331119</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>624074</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7307283</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>135331669</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Tsågávvrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>624037</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7307291</v>
+      </c>
+      <c r="S96" t="n">
+        <v>6</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>135332778</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Tsågávvrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>623849</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7307318</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>135333180</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>623673</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7307275</v>
+      </c>
+      <c r="S98" t="n">
+        <v>7</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>135333382</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Tsågávvrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>624084</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7307323</v>
+      </c>
+      <c r="S99" t="n">
+        <v>6</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
           <t>Linda Nordström</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
+      <c r="AX99" t="inlineStr">
         <is>
           <t>Linda Nordström</t>
         </is>
       </c>
-      <c r="AY92" t="inlineStr">
+      <c r="AY99" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY99"/>
+  <dimension ref="A1:AY100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6839,7 +6839,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135331670</v>
+        <v>135331350</v>
       </c>
       <c r="B58" t="n">
         <v>79373</v>
@@ -6870,17 +6870,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>624012</v>
+        <v>623938</v>
       </c>
       <c r="R58" t="n">
-        <v>7307326</v>
+        <v>7307328</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6934,12 +6934,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6950,48 +6950,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135331033</v>
+        <v>135331670</v>
       </c>
       <c r="B59" t="n">
-        <v>78776</v>
+        <v>79373</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>623649</v>
+        <v>624012</v>
       </c>
       <c r="R59" t="n">
-        <v>7307278</v>
+        <v>7307326</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7018,9 +7018,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7035,12 +7045,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7051,7 +7061,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135333364</v>
+        <v>135331033</v>
       </c>
       <c r="B60" t="n">
         <v>78776</v>
@@ -7082,14 +7092,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>624037</v>
+        <v>623649</v>
       </c>
       <c r="R60" t="n">
-        <v>7307285</v>
+        <v>7307278</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7119,19 +7129,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>15:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7146,12 +7146,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7162,7 +7162,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135333375</v>
+        <v>135333364</v>
       </c>
       <c r="B61" t="n">
         <v>78776</v>
@@ -7197,13 +7197,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>623832</v>
+        <v>624037</v>
       </c>
       <c r="R61" t="n">
-        <v>7307315</v>
+        <v>7307285</v>
       </c>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7273,10 +7273,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135332772</v>
+        <v>135333375</v>
       </c>
       <c r="B62" t="n">
-        <v>83358</v>
+        <v>78776</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7284,21 +7284,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7308,13 +7308,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>624017</v>
+        <v>623832</v>
       </c>
       <c r="R62" t="n">
-        <v>7307324</v>
+        <v>7307315</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7368,12 +7368,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7384,7 +7384,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135332775</v>
+        <v>135332772</v>
       </c>
       <c r="B63" t="n">
         <v>83358</v>
@@ -7419,13 +7419,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>623971</v>
+        <v>624017</v>
       </c>
       <c r="R63" t="n">
-        <v>7307331</v>
+        <v>7307324</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7495,10 +7495,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135331035</v>
+        <v>135332775</v>
       </c>
       <c r="B64" t="n">
-        <v>79992</v>
+        <v>83358</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7506,37 +7506,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>623629</v>
+        <v>623971</v>
       </c>
       <c r="R64" t="n">
-        <v>7307251</v>
+        <v>7307331</v>
       </c>
       <c r="S64" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7563,9 +7563,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7580,12 +7590,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7596,7 +7606,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135332771</v>
+        <v>135331035</v>
       </c>
       <c r="B65" t="n">
         <v>79992</v>
@@ -7627,17 +7637,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>624036</v>
+        <v>623629</v>
       </c>
       <c r="R65" t="n">
-        <v>7307307</v>
+        <v>7307251</v>
       </c>
       <c r="S65" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7664,19 +7674,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>15:44</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7691,12 +7691,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7707,7 +7707,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135332776</v>
+        <v>135332771</v>
       </c>
       <c r="B66" t="n">
         <v>79992</v>
@@ -7742,13 +7742,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>623926</v>
+        <v>624036</v>
       </c>
       <c r="R66" t="n">
-        <v>7307301</v>
+        <v>7307307</v>
       </c>
       <c r="S66" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7818,7 +7818,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135333181</v>
+        <v>135332776</v>
       </c>
       <c r="B67" t="n">
         <v>79992</v>
@@ -7849,17 +7849,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>623638</v>
+        <v>623926</v>
       </c>
       <c r="R67" t="n">
-        <v>7307259</v>
+        <v>7307301</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7913,12 +7913,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7929,48 +7929,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135333371</v>
+        <v>135333181</v>
       </c>
       <c r="B68" t="n">
-        <v>57972</v>
+        <v>79992</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>624014</v>
+        <v>623638</v>
       </c>
       <c r="R68" t="n">
-        <v>7307360</v>
+        <v>7307259</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8024,12 +8024,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8040,7 +8040,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135333374</v>
+        <v>135333371</v>
       </c>
       <c r="B69" t="n">
         <v>57972</v>
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>623919</v>
+        <v>624014</v>
       </c>
       <c r="R69" t="n">
-        <v>7307361</v>
+        <v>7307360</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8120,12 +8120,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8156,27 +8151,27 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135318090</v>
+        <v>135333374</v>
       </c>
       <c r="B70" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8187,17 +8182,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>623800</v>
+        <v>623919</v>
       </c>
       <c r="R70" t="n">
-        <v>7307412</v>
+        <v>7307361</v>
       </c>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8226,7 +8221,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8236,7 +8231,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8251,19 +8251,23 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135331038</v>
+        <v>135318090</v>
       </c>
       <c r="B71" t="n">
         <v>57975</v>
@@ -8294,17 +8298,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>623589</v>
+        <v>623800</v>
       </c>
       <c r="R71" t="n">
-        <v>7307264</v>
+        <v>7307412</v>
       </c>
       <c r="S71" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8331,14 +8335,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8353,23 +8362,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135332777</v>
+        <v>135331038</v>
       </c>
       <c r="B72" t="n">
         <v>57975</v>
@@ -8398,24 +8403,19 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>623904</v>
+        <v>623589</v>
       </c>
       <c r="R72" t="n">
-        <v>7307334</v>
+        <v>7307264</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8442,19 +8442,14 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>16:10</t>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8469,12 +8464,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8485,7 +8480,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135332781</v>
+        <v>135332777</v>
       </c>
       <c r="B73" t="n">
         <v>57975</v>
@@ -8525,10 +8520,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>623790</v>
+        <v>623904</v>
       </c>
       <c r="R73" t="n">
-        <v>7307346</v>
+        <v>7307334</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8560,7 +8555,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8570,7 +8565,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8601,7 +8596,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135332783</v>
+        <v>135332781</v>
       </c>
       <c r="B74" t="n">
         <v>57975</v>
@@ -8630,19 +8625,24 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>623971</v>
+        <v>623790</v>
       </c>
       <c r="R74" t="n">
-        <v>7307384</v>
+        <v>7307346</v>
       </c>
       <c r="S74" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8681,19 +8681,14 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>skalade undertryckta granar, flera stycken</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="b">
         <v>0</v>
@@ -8717,7 +8712,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135332786</v>
+        <v>135332783</v>
       </c>
       <c r="B75" t="n">
         <v>57975</v>
@@ -8746,24 +8741,19 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>624077</v>
+        <v>623971</v>
       </c>
       <c r="R75" t="n">
-        <v>7307313</v>
+        <v>7307384</v>
       </c>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8792,7 +8782,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8802,14 +8792,19 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>skalade undertryckta granar, flera stycken</t>
         </is>
       </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG75" t="b">
         <v>0</v>
@@ -8833,7 +8828,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135333182</v>
+        <v>135332786</v>
       </c>
       <c r="B76" t="n">
         <v>57975</v>
@@ -8862,19 +8857,24 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>623602</v>
+        <v>624077</v>
       </c>
       <c r="R76" t="n">
-        <v>7307284</v>
+        <v>7307313</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8913,12 +8913,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8933,12 +8928,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8949,7 +8944,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135337852</v>
+        <v>135333182</v>
       </c>
       <c r="B77" t="n">
         <v>57975</v>
@@ -8980,14 +8975,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>623747</v>
+        <v>623602</v>
       </c>
       <c r="R77" t="n">
-        <v>7307427</v>
+        <v>7307284</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9019,7 +9014,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9029,12 +9024,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9049,12 +9044,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9065,45 +9060,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135331121</v>
+        <v>135337852</v>
       </c>
       <c r="B78" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>623943</v>
+        <v>623747</v>
       </c>
       <c r="R78" t="n">
-        <v>7307296</v>
+        <v>7307427</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9135,7 +9130,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9145,7 +9140,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9160,12 +9160,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9176,7 +9176,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135331122</v>
+        <v>135331121</v>
       </c>
       <c r="B79" t="n">
         <v>57162</v>
@@ -9211,10 +9211,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>623926</v>
+        <v>623943</v>
       </c>
       <c r="R79" t="n">
-        <v>7307337</v>
+        <v>7307296</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9256,12 +9256,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Tjäderbo? eller uppehallsplats?</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9292,10 +9287,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135331032</v>
+        <v>135331122</v>
       </c>
       <c r="B80" t="n">
-        <v>5181</v>
+        <v>57162</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9303,37 +9298,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>623649</v>
+        <v>623926</v>
       </c>
       <c r="R80" t="n">
-        <v>7307278</v>
+        <v>7307337</v>
       </c>
       <c r="S80" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9360,14 +9355,24 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Gnag</t>
+          <t>Tjäderbo? eller uppehallsplats?</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9382,12 +9387,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9398,7 +9403,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135333376</v>
+        <v>135331032</v>
       </c>
       <c r="B81" t="n">
         <v>5181</v>
@@ -9429,17 +9434,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>623799</v>
+        <v>623649</v>
       </c>
       <c r="R81" t="n">
-        <v>7307327</v>
+        <v>7307278</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9466,19 +9471,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>16:20</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -9498,12 +9493,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9514,32 +9509,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135332770</v>
+        <v>135333376</v>
       </c>
       <c r="B82" t="n">
-        <v>58136</v>
+        <v>5181</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9549,13 +9544,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>624031</v>
+        <v>623799</v>
       </c>
       <c r="R82" t="n">
-        <v>7307306</v>
+        <v>7307327</v>
       </c>
       <c r="S82" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9584,7 +9579,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9594,7 +9589,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9609,12 +9609,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9625,7 +9625,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135333365</v>
+        <v>135332770</v>
       </c>
       <c r="B83" t="n">
         <v>58136</v>
@@ -9660,13 +9660,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>624039</v>
+        <v>624031</v>
       </c>
       <c r="R83" t="n">
-        <v>7307316</v>
+        <v>7307306</v>
       </c>
       <c r="S83" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9720,12 +9720,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9736,7 +9736,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135333378</v>
+        <v>135333365</v>
       </c>
       <c r="B84" t="n">
         <v>58136</v>
@@ -9771,13 +9771,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>624079</v>
+        <v>624039</v>
       </c>
       <c r="R84" t="n">
-        <v>7307360</v>
+        <v>7307316</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9816,12 +9816,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Familjegrupp, minst 5 st</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9852,48 +9847,48 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135331030</v>
+        <v>135333378</v>
       </c>
       <c r="B85" t="n">
-        <v>5201</v>
+        <v>58136</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>623665</v>
+        <v>624079</v>
       </c>
       <c r="R85" t="n">
-        <v>7307294</v>
+        <v>7307360</v>
       </c>
       <c r="S85" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9920,14 +9915,24 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Gnag</t>
+          <t>Familjegrupp, minst 5 st</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9942,12 +9947,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9958,10 +9963,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135333372</v>
+        <v>135331030</v>
       </c>
       <c r="B86" t="n">
-        <v>99099</v>
+        <v>5201</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9969,37 +9974,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220093</v>
+        <v>105930</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>624008</v>
+        <v>623665</v>
       </c>
       <c r="R86" t="n">
-        <v>7307352</v>
+        <v>7307294</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10026,24 +10031,14 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Kolla</t>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10058,12 +10053,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -10074,10 +10069,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135331671</v>
+        <v>135333372</v>
       </c>
       <c r="B87" t="n">
-        <v>98060</v>
+        <v>99099</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10085,34 +10080,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221945</v>
+        <v>220093</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>623997</v>
+        <v>624008</v>
       </c>
       <c r="R87" t="n">
-        <v>7307348</v>
+        <v>7307352</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10144,7 +10139,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10154,7 +10149,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Kolla</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10169,12 +10169,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10185,10 +10185,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135331145</v>
+        <v>135331671</v>
       </c>
       <c r="B88" t="n">
-        <v>99217</v>
+        <v>98060</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10196,37 +10196,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>623644</v>
+        <v>623997</v>
       </c>
       <c r="R88" t="n">
-        <v>7307354</v>
+        <v>7307348</v>
       </c>
       <c r="S88" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10280,12 +10280,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -10296,7 +10296,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135331672</v>
+        <v>135331145</v>
       </c>
       <c r="B89" t="n">
         <v>99217</v>
@@ -10327,17 +10327,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>624001</v>
+        <v>623644</v>
       </c>
       <c r="R89" t="n">
-        <v>7307352</v>
+        <v>7307354</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10391,12 +10391,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -10407,7 +10407,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135331673</v>
+        <v>135331672</v>
       </c>
       <c r="B90" t="n">
         <v>99217</v>
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>623969</v>
+        <v>624001</v>
       </c>
       <c r="R90" t="n">
-        <v>7307338</v>
+        <v>7307352</v>
       </c>
       <c r="S90" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10518,7 +10518,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135331674</v>
+        <v>135331673</v>
       </c>
       <c r="B91" t="n">
         <v>99217</v>
@@ -10553,13 +10553,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>623948</v>
+        <v>623969</v>
       </c>
       <c r="R91" t="n">
-        <v>7307327</v>
+        <v>7307338</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10629,48 +10629,48 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135331039</v>
+        <v>135331674</v>
       </c>
       <c r="B92" t="n">
-        <v>79963</v>
+        <v>99217</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>623714</v>
+        <v>623948</v>
       </c>
       <c r="R92" t="n">
-        <v>7307148</v>
+        <v>7307327</v>
       </c>
       <c r="S92" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10697,9 +10697,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10714,12 +10724,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10730,7 +10740,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135331124</v>
+        <v>135331039</v>
       </c>
       <c r="B93" t="n">
         <v>79963</v>
@@ -10761,17 +10771,17 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>623675</v>
+        <v>623714</v>
       </c>
       <c r="R93" t="n">
-        <v>7307271</v>
+        <v>7307148</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10798,19 +10808,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10825,12 +10825,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10841,7 +10841,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135331125</v>
+        <v>135331124</v>
       </c>
       <c r="B94" t="n">
         <v>79963</v>
@@ -10876,13 +10876,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>623635</v>
+        <v>623675</v>
       </c>
       <c r="R94" t="n">
-        <v>7307226</v>
+        <v>7307271</v>
       </c>
       <c r="S94" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10921,12 +10921,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Stubbe med yxhugg ser bild</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10957,10 +10952,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135331119</v>
+        <v>135331125</v>
       </c>
       <c r="B95" t="n">
-        <v>79396</v>
+        <v>79963</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10968,21 +10963,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10992,13 +10987,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>624074</v>
+        <v>623635</v>
       </c>
       <c r="R95" t="n">
-        <v>7307283</v>
+        <v>7307226</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11027,7 +11022,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11037,7 +11032,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Stubbe med yxhugg ser bild</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11046,7 +11046,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11069,7 +11068,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135331669</v>
+        <v>135331119</v>
       </c>
       <c r="B96" t="n">
         <v>79396</v>
@@ -11100,17 +11099,17 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>624037</v>
+        <v>624074</v>
       </c>
       <c r="R96" t="n">
-        <v>7307291</v>
+        <v>7307283</v>
       </c>
       <c r="S96" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11139,7 +11138,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11149,7 +11148,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11158,18 +11157,19 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -11180,7 +11180,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135332778</v>
+        <v>135331669</v>
       </c>
       <c r="B97" t="n">
         <v>79396</v>
@@ -11211,17 +11211,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>623849</v>
+        <v>624037</v>
       </c>
       <c r="R97" t="n">
-        <v>7307318</v>
+        <v>7307291</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11260,7 +11260,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11275,12 +11275,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -11291,7 +11291,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135333180</v>
+        <v>135332778</v>
       </c>
       <c r="B98" t="n">
         <v>79396</v>
@@ -11322,17 +11322,17 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>623673</v>
+        <v>623849</v>
       </c>
       <c r="R98" t="n">
-        <v>7307275</v>
+        <v>7307318</v>
       </c>
       <c r="S98" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11386,12 +11386,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11402,7 +11402,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135333382</v>
+        <v>135333180</v>
       </c>
       <c r="B99" t="n">
         <v>79396</v>
@@ -11433,17 +11433,17 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>624084</v>
+        <v>623673</v>
       </c>
       <c r="R99" t="n">
-        <v>7307323</v>
+        <v>7307275</v>
       </c>
       <c r="S99" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11497,15 +11497,126 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>135333382</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Tsågávvrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>624084</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7307323</v>
+      </c>
+      <c r="S100" t="n">
+        <v>6</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
           <t>Linda Nordström</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
+      <c r="AX100" t="inlineStr">
         <is>
           <t>Linda Nordström</t>
         </is>
       </c>
-      <c r="AY99" t="inlineStr">
+      <c r="AY100" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
@@ -2382,7 +2382,7 @@
         <v>623499</v>
       </c>
       <c r="R17" t="n">
-        <v>7307488</v>
+        <v>7307487</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>

--- a/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY100"/>
+  <dimension ref="A1:AY101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7384,10 +7384,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135332772</v>
+        <v>135358216</v>
       </c>
       <c r="B63" t="n">
-        <v>83358</v>
+        <v>78776</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7395,21 +7395,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7419,13 +7419,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>624017</v>
+        <v>624015</v>
       </c>
       <c r="R63" t="n">
-        <v>7307324</v>
+        <v>7307320</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7479,12 +7479,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7495,7 +7495,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135332775</v>
+        <v>135332772</v>
       </c>
       <c r="B64" t="n">
         <v>83358</v>
@@ -7530,13 +7530,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>623971</v>
+        <v>624017</v>
       </c>
       <c r="R64" t="n">
-        <v>7307331</v>
+        <v>7307324</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7606,10 +7606,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135331035</v>
+        <v>135332775</v>
       </c>
       <c r="B65" t="n">
-        <v>79992</v>
+        <v>83358</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7617,37 +7617,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>623629</v>
+        <v>623971</v>
       </c>
       <c r="R65" t="n">
-        <v>7307251</v>
+        <v>7307331</v>
       </c>
       <c r="S65" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7674,9 +7674,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7691,12 +7701,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7707,7 +7717,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135332771</v>
+        <v>135331035</v>
       </c>
       <c r="B66" t="n">
         <v>79992</v>
@@ -7738,17 +7748,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>624036</v>
+        <v>623629</v>
       </c>
       <c r="R66" t="n">
-        <v>7307307</v>
+        <v>7307251</v>
       </c>
       <c r="S66" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7775,19 +7785,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:44</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7802,12 +7802,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7818,7 +7818,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135332776</v>
+        <v>135332771</v>
       </c>
       <c r="B67" t="n">
         <v>79992</v>
@@ -7853,13 +7853,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>623926</v>
+        <v>624036</v>
       </c>
       <c r="R67" t="n">
-        <v>7307301</v>
+        <v>7307307</v>
       </c>
       <c r="S67" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7929,7 +7929,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135333181</v>
+        <v>135332776</v>
       </c>
       <c r="B68" t="n">
         <v>79992</v>
@@ -7960,17 +7960,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>623638</v>
+        <v>623926</v>
       </c>
       <c r="R68" t="n">
-        <v>7307259</v>
+        <v>7307301</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8024,12 +8024,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8040,48 +8040,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135333371</v>
+        <v>135333181</v>
       </c>
       <c r="B69" t="n">
-        <v>57972</v>
+        <v>79992</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>624014</v>
+        <v>623638</v>
       </c>
       <c r="R69" t="n">
-        <v>7307360</v>
+        <v>7307259</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8135,12 +8135,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8151,7 +8151,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135333374</v>
+        <v>135333371</v>
       </c>
       <c r="B70" t="n">
         <v>57972</v>
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>623919</v>
+        <v>624014</v>
       </c>
       <c r="R70" t="n">
-        <v>7307361</v>
+        <v>7307360</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8221,7 +8221,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8231,12 +8231,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8267,27 +8262,27 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135318090</v>
+        <v>135333374</v>
       </c>
       <c r="B71" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8298,17 +8293,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>623800</v>
+        <v>623919</v>
       </c>
       <c r="R71" t="n">
-        <v>7307412</v>
+        <v>7307361</v>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8337,7 +8332,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8347,7 +8342,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8362,19 +8362,23 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135331038</v>
+        <v>135318090</v>
       </c>
       <c r="B72" t="n">
         <v>57975</v>
@@ -8405,17 +8409,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>623589</v>
+        <v>623800</v>
       </c>
       <c r="R72" t="n">
-        <v>7307264</v>
+        <v>7307412</v>
       </c>
       <c r="S72" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8442,14 +8446,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8464,23 +8473,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135332777</v>
+        <v>135331038</v>
       </c>
       <c r="B73" t="n">
         <v>57975</v>
@@ -8509,24 +8514,19 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>623904</v>
+        <v>623589</v>
       </c>
       <c r="R73" t="n">
-        <v>7307334</v>
+        <v>7307264</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8553,19 +8553,14 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>16:10</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8580,12 +8575,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8596,7 +8591,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135332781</v>
+        <v>135332777</v>
       </c>
       <c r="B74" t="n">
         <v>57975</v>
@@ -8636,10 +8631,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>623790</v>
+        <v>623904</v>
       </c>
       <c r="R74" t="n">
-        <v>7307346</v>
+        <v>7307334</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8671,7 +8666,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8681,7 +8676,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8712,7 +8707,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135332783</v>
+        <v>135332781</v>
       </c>
       <c r="B75" t="n">
         <v>57975</v>
@@ -8741,19 +8736,24 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>623971</v>
+        <v>623790</v>
       </c>
       <c r="R75" t="n">
-        <v>7307384</v>
+        <v>7307346</v>
       </c>
       <c r="S75" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8792,19 +8792,14 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>skalade undertryckta granar, flera stycken</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="b">
         <v>0</v>
@@ -8828,7 +8823,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135332786</v>
+        <v>135332783</v>
       </c>
       <c r="B76" t="n">
         <v>57975</v>
@@ -8857,24 +8852,19 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>624077</v>
+        <v>623971</v>
       </c>
       <c r="R76" t="n">
-        <v>7307313</v>
+        <v>7307384</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8903,7 +8893,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8913,14 +8903,19 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>skalade undertryckta granar, flera stycken</t>
         </is>
       </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG76" t="b">
         <v>0</v>
@@ -8944,7 +8939,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135333182</v>
+        <v>135332786</v>
       </c>
       <c r="B77" t="n">
         <v>57975</v>
@@ -8973,19 +8968,24 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>623602</v>
+        <v>624077</v>
       </c>
       <c r="R77" t="n">
-        <v>7307284</v>
+        <v>7307313</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9024,12 +9024,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9044,12 +9039,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9060,7 +9055,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135337852</v>
+        <v>135333182</v>
       </c>
       <c r="B78" t="n">
         <v>57975</v>
@@ -9091,14 +9086,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>623747</v>
+        <v>623602</v>
       </c>
       <c r="R78" t="n">
-        <v>7307427</v>
+        <v>7307284</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9130,7 +9125,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9140,12 +9135,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9160,12 +9155,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9176,45 +9171,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135331121</v>
+        <v>135337852</v>
       </c>
       <c r="B79" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>623943</v>
+        <v>623747</v>
       </c>
       <c r="R79" t="n">
-        <v>7307296</v>
+        <v>7307427</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9246,7 +9241,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9256,7 +9251,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9271,12 +9271,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9287,7 +9287,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135331122</v>
+        <v>135331121</v>
       </c>
       <c r="B80" t="n">
         <v>57162</v>
@@ -9322,10 +9322,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>623926</v>
+        <v>623943</v>
       </c>
       <c r="R80" t="n">
-        <v>7307337</v>
+        <v>7307296</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9357,7 +9357,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9367,12 +9367,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Tjäderbo? eller uppehallsplats?</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9403,10 +9398,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135331032</v>
+        <v>135331122</v>
       </c>
       <c r="B81" t="n">
-        <v>5181</v>
+        <v>57162</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9414,37 +9409,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>623649</v>
+        <v>623926</v>
       </c>
       <c r="R81" t="n">
-        <v>7307278</v>
+        <v>7307337</v>
       </c>
       <c r="S81" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9471,14 +9466,24 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Gnag</t>
+          <t>Tjäderbo? eller uppehallsplats?</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9493,12 +9498,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9509,7 +9514,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135333376</v>
+        <v>135331032</v>
       </c>
       <c r="B82" t="n">
         <v>5181</v>
@@ -9540,17 +9545,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>623799</v>
+        <v>623649</v>
       </c>
       <c r="R82" t="n">
-        <v>7307327</v>
+        <v>7307278</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9577,19 +9582,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>16:20</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -9609,12 +9604,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9625,32 +9620,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135332770</v>
+        <v>135333376</v>
       </c>
       <c r="B83" t="n">
-        <v>58136</v>
+        <v>5181</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9660,13 +9655,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>624031</v>
+        <v>623799</v>
       </c>
       <c r="R83" t="n">
-        <v>7307306</v>
+        <v>7307327</v>
       </c>
       <c r="S83" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9695,7 +9690,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9705,7 +9700,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9720,12 +9720,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9736,7 +9736,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135333365</v>
+        <v>135332770</v>
       </c>
       <c r="B84" t="n">
         <v>58136</v>
@@ -9771,13 +9771,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>624039</v>
+        <v>624031</v>
       </c>
       <c r="R84" t="n">
-        <v>7307316</v>
+        <v>7307306</v>
       </c>
       <c r="S84" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9831,12 +9831,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9847,7 +9847,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135333378</v>
+        <v>135333365</v>
       </c>
       <c r="B85" t="n">
         <v>58136</v>
@@ -9882,13 +9882,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>624079</v>
+        <v>624039</v>
       </c>
       <c r="R85" t="n">
-        <v>7307360</v>
+        <v>7307316</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9927,12 +9927,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Familjegrupp, minst 5 st</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9963,48 +9958,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135331030</v>
+        <v>135333378</v>
       </c>
       <c r="B86" t="n">
-        <v>5201</v>
+        <v>58136</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>623665</v>
+        <v>624079</v>
       </c>
       <c r="R86" t="n">
-        <v>7307294</v>
+        <v>7307360</v>
       </c>
       <c r="S86" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10031,14 +10026,24 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Gnag</t>
+          <t>Familjegrupp, minst 5 st</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10053,12 +10058,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -10069,10 +10074,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135333372</v>
+        <v>135331030</v>
       </c>
       <c r="B87" t="n">
-        <v>99099</v>
+        <v>5201</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10080,37 +10085,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220093</v>
+        <v>105930</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>624008</v>
+        <v>623665</v>
       </c>
       <c r="R87" t="n">
-        <v>7307352</v>
+        <v>7307294</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10137,24 +10142,14 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Kolla</t>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10169,12 +10164,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10185,10 +10180,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135331671</v>
+        <v>135333372</v>
       </c>
       <c r="B88" t="n">
-        <v>98060</v>
+        <v>99099</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10196,34 +10191,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221945</v>
+        <v>220093</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>623997</v>
+        <v>624008</v>
       </c>
       <c r="R88" t="n">
-        <v>7307348</v>
+        <v>7307352</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10255,7 +10250,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10265,7 +10260,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Kolla</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10280,12 +10280,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -10296,10 +10296,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135331145</v>
+        <v>135331671</v>
       </c>
       <c r="B89" t="n">
-        <v>99217</v>
+        <v>98060</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10307,37 +10307,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>623644</v>
+        <v>623997</v>
       </c>
       <c r="R89" t="n">
-        <v>7307354</v>
+        <v>7307348</v>
       </c>
       <c r="S89" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10391,12 +10391,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -10407,7 +10407,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135331672</v>
+        <v>135331145</v>
       </c>
       <c r="B90" t="n">
         <v>99217</v>
@@ -10438,17 +10438,17 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>624001</v>
+        <v>623644</v>
       </c>
       <c r="R90" t="n">
-        <v>7307352</v>
+        <v>7307354</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10502,12 +10502,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -10518,7 +10518,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135331673</v>
+        <v>135331672</v>
       </c>
       <c r="B91" t="n">
         <v>99217</v>
@@ -10553,13 +10553,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>623969</v>
+        <v>624001</v>
       </c>
       <c r="R91" t="n">
-        <v>7307338</v>
+        <v>7307352</v>
       </c>
       <c r="S91" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10629,7 +10629,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135331674</v>
+        <v>135331673</v>
       </c>
       <c r="B92" t="n">
         <v>99217</v>
@@ -10664,13 +10664,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>623948</v>
+        <v>623969</v>
       </c>
       <c r="R92" t="n">
-        <v>7307327</v>
+        <v>7307338</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10740,48 +10740,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135331039</v>
+        <v>135331674</v>
       </c>
       <c r="B93" t="n">
-        <v>79963</v>
+        <v>99217</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>623714</v>
+        <v>623948</v>
       </c>
       <c r="R93" t="n">
-        <v>7307148</v>
+        <v>7307327</v>
       </c>
       <c r="S93" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10808,9 +10808,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10825,12 +10835,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10841,7 +10851,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135331124</v>
+        <v>135331039</v>
       </c>
       <c r="B94" t="n">
         <v>79963</v>
@@ -10872,17 +10882,17 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>623675</v>
+        <v>623714</v>
       </c>
       <c r="R94" t="n">
-        <v>7307271</v>
+        <v>7307148</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10909,19 +10919,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10936,12 +10936,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10952,7 +10952,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135331125</v>
+        <v>135331124</v>
       </c>
       <c r="B95" t="n">
         <v>79963</v>
@@ -10987,13 +10987,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>623635</v>
+        <v>623675</v>
       </c>
       <c r="R95" t="n">
-        <v>7307226</v>
+        <v>7307271</v>
       </c>
       <c r="S95" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11032,12 +11032,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Stubbe med yxhugg ser bild</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11068,10 +11063,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135331119</v>
+        <v>135331125</v>
       </c>
       <c r="B96" t="n">
-        <v>79396</v>
+        <v>79963</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11079,21 +11074,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11103,13 +11098,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>624074</v>
+        <v>623635</v>
       </c>
       <c r="R96" t="n">
-        <v>7307283</v>
+        <v>7307226</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11138,7 +11133,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11148,7 +11143,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Stubbe med yxhugg ser bild</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11157,7 +11157,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -11180,7 +11179,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135331669</v>
+        <v>135331119</v>
       </c>
       <c r="B97" t="n">
         <v>79396</v>
@@ -11211,17 +11210,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>624037</v>
+        <v>624074</v>
       </c>
       <c r="R97" t="n">
-        <v>7307291</v>
+        <v>7307283</v>
       </c>
       <c r="S97" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11250,7 +11249,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11260,7 +11259,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11269,18 +11268,19 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -11291,7 +11291,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135332778</v>
+        <v>135331669</v>
       </c>
       <c r="B98" t="n">
         <v>79396</v>
@@ -11322,17 +11322,17 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>623849</v>
+        <v>624037</v>
       </c>
       <c r="R98" t="n">
-        <v>7307318</v>
+        <v>7307291</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11386,12 +11386,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11402,7 +11402,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135333180</v>
+        <v>135332778</v>
       </c>
       <c r="B99" t="n">
         <v>79396</v>
@@ -11433,17 +11433,17 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>623673</v>
+        <v>623849</v>
       </c>
       <c r="R99" t="n">
-        <v>7307275</v>
+        <v>7307318</v>
       </c>
       <c r="S99" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11497,12 +11497,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11513,7 +11513,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135333382</v>
+        <v>135333180</v>
       </c>
       <c r="B100" t="n">
         <v>79396</v>
@@ -11544,17 +11544,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>624084</v>
+        <v>623673</v>
       </c>
       <c r="R100" t="n">
-        <v>7307323</v>
+        <v>7307275</v>
       </c>
       <c r="S100" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11608,15 +11608,126 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>135333382</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Tsågávvrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>624084</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7307323</v>
+      </c>
+      <c r="S101" t="n">
+        <v>6</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
           <t>Linda Nordström</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
+      <c r="AX101" t="inlineStr">
         <is>
           <t>Linda Nordström</t>
         </is>
       </c>
-      <c r="AY100" t="inlineStr">
+      <c r="AY101" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY101"/>
+  <dimension ref="A1:AY100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,32 +792,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135331130</v>
+        <v>135331133</v>
       </c>
       <c r="B3" t="n">
-        <v>79442</v>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>639</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grenlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Evernia mesomorpha</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623561</v>
+        <v>623534</v>
       </c>
       <c r="R3" t="n">
-        <v>7307299</v>
+        <v>7307322</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135331133</v>
+        <v>135331136</v>
       </c>
       <c r="B4" t="n">
         <v>92245</v>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623534</v>
+        <v>623564</v>
       </c>
       <c r="R4" t="n">
-        <v>7307322</v>
+        <v>7307337</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135331136</v>
+        <v>135333192</v>
       </c>
       <c r="B5" t="n">
         <v>92245</v>
@@ -1045,17 +1045,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623564</v>
+        <v>623498</v>
       </c>
       <c r="R5" t="n">
-        <v>7307337</v>
+        <v>7307367</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,12 +1109,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1125,32 +1125,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135333192</v>
+        <v>135333193</v>
       </c>
       <c r="B6" t="n">
-        <v>92245</v>
+        <v>92795</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>918</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,13 +1160,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623498</v>
+        <v>623559</v>
       </c>
       <c r="R6" t="n">
-        <v>7307367</v>
+        <v>7307431</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,7 +1236,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135333193</v>
+        <v>135337856</v>
       </c>
       <c r="B7" t="n">
         <v>92795</v>
@@ -1267,17 +1267,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623559</v>
+        <v>623566</v>
       </c>
       <c r="R7" t="n">
-        <v>7307431</v>
+        <v>7307479</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1316,7 +1316,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran rörligt markvatten. Har kollekt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,18 +1330,19 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1347,45 +1353,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135337856</v>
+        <v>135333195</v>
       </c>
       <c r="B8" t="n">
-        <v>92795</v>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>918</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623566</v>
+        <v>623422</v>
       </c>
       <c r="R8" t="n">
-        <v>7307479</v>
+        <v>7307495</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,7 +1423,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,12 +1433,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gran rörligt markvatten. Har kollekt</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,19 +1442,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135333195</v>
+        <v>135331141</v>
       </c>
       <c r="B9" t="n">
-        <v>91974</v>
+        <v>83222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,34 +1475,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623422</v>
+        <v>623557</v>
       </c>
       <c r="R9" t="n">
-        <v>7307495</v>
+        <v>7307476</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,12 +1559,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1575,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135331141</v>
+        <v>135331135</v>
       </c>
       <c r="B10" t="n">
-        <v>83222</v>
+        <v>92167</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,21 +1586,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>1588</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623557</v>
+        <v>623561</v>
       </c>
       <c r="R10" t="n">
-        <v>7307476</v>
+        <v>7307325</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,7 +1686,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135331135</v>
+        <v>135331140</v>
       </c>
       <c r="B11" t="n">
         <v>92167</v>
@@ -1721,13 +1721,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623561</v>
+        <v>623575</v>
       </c>
       <c r="R11" t="n">
-        <v>7307325</v>
+        <v>7307427</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1797,32 +1797,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135331140</v>
+        <v>135331131</v>
       </c>
       <c r="B12" t="n">
-        <v>92167</v>
+        <v>96678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1588</v>
+        <v>2166</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1832,13 +1832,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623575</v>
+        <v>623557</v>
       </c>
       <c r="R12" t="n">
-        <v>7307427</v>
+        <v>7307301</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135331131</v>
+        <v>135331132</v>
       </c>
       <c r="B13" t="n">
-        <v>96678</v>
+        <v>97308</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2166</v>
+        <v>2869</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623557</v>
+        <v>623545</v>
       </c>
       <c r="R13" t="n">
-        <v>7307301</v>
+        <v>7307305</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135331132</v>
+        <v>135320627</v>
       </c>
       <c r="B14" t="n">
-        <v>97308</v>
+        <v>91937</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,37 +2030,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2869</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623545</v>
+        <v>623517</v>
       </c>
       <c r="R14" t="n">
-        <v>7307305</v>
+        <v>7307459</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,48 +2114,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135320627</v>
+        <v>135319473</v>
       </c>
       <c r="B15" t="n">
-        <v>91937</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2165,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623517</v>
+        <v>623472</v>
       </c>
       <c r="R15" t="n">
-        <v>7307459</v>
+        <v>7307510</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2200,7 +2196,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2206,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,7 +2233,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135319473</v>
+        <v>135319562</v>
       </c>
       <c r="B16" t="n">
         <v>79373</v>
@@ -2272,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623472</v>
+        <v>623499</v>
       </c>
       <c r="R16" t="n">
-        <v>7307510</v>
+        <v>7307487</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2307,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2317,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,7 +2340,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135319562</v>
+        <v>135333184</v>
       </c>
       <c r="B17" t="n">
         <v>79373</v>
@@ -2375,17 +2371,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623499</v>
+        <v>623581</v>
       </c>
       <c r="R17" t="n">
-        <v>7307487</v>
+        <v>7307301</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2414,7 +2410,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2424,7 +2420,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2439,19 +2435,23 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135333184</v>
+        <v>135333188</v>
       </c>
       <c r="B18" t="n">
         <v>79373</v>
@@ -2486,13 +2486,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623581</v>
+        <v>623541</v>
       </c>
       <c r="R18" t="n">
-        <v>7307301</v>
+        <v>7307359</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2562,7 +2562,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135333188</v>
+        <v>135333190</v>
       </c>
       <c r="B19" t="n">
         <v>79373</v>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623541</v>
+        <v>623521</v>
       </c>
       <c r="R19" t="n">
-        <v>7307359</v>
+        <v>7307382</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2673,48 +2673,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135333190</v>
+        <v>135320009</v>
       </c>
       <c r="B20" t="n">
-        <v>79373</v>
+        <v>78776</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623521</v>
+        <v>623461</v>
       </c>
       <c r="R20" t="n">
-        <v>7307382</v>
+        <v>7307589</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2768,26 +2768,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135320009</v>
+        <v>135333183</v>
       </c>
       <c r="B21" t="n">
-        <v>78776</v>
+        <v>83358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2795,37 +2791,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623461</v>
+        <v>623578</v>
       </c>
       <c r="R21" t="n">
-        <v>7307589</v>
+        <v>7307305</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2854,7 +2850,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2864,7 +2860,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2879,22 +2875,26 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135333183</v>
+        <v>135319971</v>
       </c>
       <c r="B22" t="n">
-        <v>83358</v>
+        <v>79992</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2902,37 +2902,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623578</v>
+        <v>623461</v>
       </c>
       <c r="R22" t="n">
-        <v>7307305</v>
+        <v>7307589</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2986,23 +2986,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135319971</v>
+        <v>135333185</v>
       </c>
       <c r="B23" t="n">
         <v>79992</v>
@@ -3033,17 +3029,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>623461</v>
+        <v>623521</v>
       </c>
       <c r="R23" t="n">
-        <v>7307589</v>
+        <v>7307328</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3072,7 +3068,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3082,7 +3078,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3097,44 +3093,48 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135333185</v>
+        <v>135333191</v>
       </c>
       <c r="B24" t="n">
-        <v>79992</v>
+        <v>80500</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3144,13 +3144,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623521</v>
+        <v>623500</v>
       </c>
       <c r="R24" t="n">
-        <v>7307328</v>
+        <v>7307377</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3220,48 +3220,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135333191</v>
+        <v>135319479</v>
       </c>
       <c r="B25" t="n">
-        <v>80500</v>
+        <v>57975</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>623500</v>
+        <v>623472</v>
       </c>
       <c r="R25" t="n">
-        <v>7307377</v>
+        <v>7307510</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3300,7 +3300,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3315,23 +3320,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135319479</v>
+        <v>135319812</v>
       </c>
       <c r="B26" t="n">
         <v>57975</v>
@@ -3366,10 +3367,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>623472</v>
+        <v>623492</v>
       </c>
       <c r="R26" t="n">
-        <v>7307510</v>
+        <v>7307534</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3401,7 +3402,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3411,7 +3412,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3443,7 +3444,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135319812</v>
+        <v>135320195</v>
       </c>
       <c r="B27" t="n">
         <v>57975</v>
@@ -3478,10 +3479,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>623492</v>
+        <v>623500</v>
       </c>
       <c r="R27" t="n">
-        <v>7307534</v>
+        <v>7307689</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3513,7 +3514,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3523,7 +3524,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3555,7 +3556,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135320195</v>
+        <v>135320511</v>
       </c>
       <c r="B28" t="n">
         <v>57975</v>
@@ -3590,10 +3591,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>623500</v>
+        <v>623489</v>
       </c>
       <c r="R28" t="n">
-        <v>7307689</v>
+        <v>7307496</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3625,7 +3626,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3635,12 +3636,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Spår</t>
+          <t>Gamla spår</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3667,7 +3668,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135320511</v>
+        <v>135337854</v>
       </c>
       <c r="B29" t="n">
         <v>57975</v>
@@ -3698,17 +3699,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>623489</v>
+        <v>623570</v>
       </c>
       <c r="R29" t="n">
-        <v>7307496</v>
+        <v>7307448</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3737,7 +3738,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3747,12 +3748,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Gamla spår</t>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3775,11 +3776,15 @@
           <t>Ulrika Karlsson</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135337854</v>
+        <v>135337855</v>
       </c>
       <c r="B30" t="n">
         <v>57975</v>
@@ -3814,10 +3819,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>623570</v>
+        <v>623573</v>
       </c>
       <c r="R30" t="n">
-        <v>7307448</v>
+        <v>7307467</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3849,7 +3854,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3859,7 +3864,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3895,7 +3900,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135337855</v>
+        <v>135337857</v>
       </c>
       <c r="B31" t="n">
         <v>57975</v>
@@ -3924,6 +3929,10 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
@@ -3933,7 +3942,7 @@
         <v>623573</v>
       </c>
       <c r="R31" t="n">
-        <v>7307467</v>
+        <v>7307487</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3965,7 +3974,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3975,12 +3984,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Spår</t>
+          <t>Spår på två träd</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4011,39 +4020,35 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135337857</v>
+        <v>135337862</v>
       </c>
       <c r="B32" t="n">
-        <v>57975</v>
+        <v>106309</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
@@ -4053,10 +4058,10 @@
         <v>623573</v>
       </c>
       <c r="R32" t="n">
-        <v>7307487</v>
+        <v>7307459</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4080,27 +4085,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Spår på två träd</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4131,10 +4131,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135337862</v>
+        <v>135319835</v>
       </c>
       <c r="B33" t="n">
-        <v>106309</v>
+        <v>98060</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4142,37 +4142,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>623573</v>
+        <v>623492</v>
       </c>
       <c r="R33" t="n">
-        <v>7307459</v>
+        <v>7307534</v>
       </c>
       <c r="S33" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4196,22 +4196,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4234,56 +4234,52 @@
           <t>Ulrika Karlsson</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135319835</v>
+        <v>135331126</v>
       </c>
       <c r="B34" t="n">
-        <v>98060</v>
+        <v>79963</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>623492</v>
+        <v>623584</v>
       </c>
       <c r="R34" t="n">
-        <v>7307534</v>
+        <v>7307249</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4312,7 +4308,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4322,7 +4318,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4337,19 +4333,23 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Laura Dobrandt</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135331126</v>
+        <v>135331128</v>
       </c>
       <c r="B35" t="n">
         <v>79963</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>623584</v>
+        <v>623566</v>
       </c>
       <c r="R35" t="n">
-        <v>7307249</v>
+        <v>7307255</v>
       </c>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4460,7 +4460,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135331128</v>
+        <v>135333186</v>
       </c>
       <c r="B36" t="n">
         <v>79963</v>
@@ -4491,14 +4491,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>623566</v>
+        <v>623526</v>
       </c>
       <c r="R36" t="n">
-        <v>7307255</v>
+        <v>7307330</v>
       </c>
       <c r="S36" t="n">
         <v>6</v>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4555,12 +4555,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4571,10 +4571,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135333186</v>
+        <v>135331143</v>
       </c>
       <c r="B37" t="n">
-        <v>79963</v>
+        <v>83350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4582,37 +4582,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>623526</v>
+        <v>623620</v>
       </c>
       <c r="R37" t="n">
-        <v>7307330</v>
+        <v>7307390</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4666,12 +4666,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4682,10 +4682,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135331143</v>
+        <v>135331036</v>
       </c>
       <c r="B38" t="n">
-        <v>83350</v>
+        <v>79039</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4693,37 +4693,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>308</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>623620</v>
+        <v>623619</v>
       </c>
       <c r="R38" t="n">
-        <v>7307390</v>
+        <v>7307249</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4750,19 +4750,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>16:16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4777,12 +4767,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4793,7 +4783,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135331036</v>
+        <v>135332782</v>
       </c>
       <c r="B39" t="n">
         <v>79039</v>
@@ -4824,17 +4814,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>623619</v>
+        <v>623828</v>
       </c>
       <c r="R39" t="n">
-        <v>7307249</v>
+        <v>7307383</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4861,9 +4851,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4878,12 +4878,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4894,45 +4894,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135332782</v>
+        <v>135331144</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>83349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>492</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>623828</v>
+        <v>623602</v>
       </c>
       <c r="R40" t="n">
-        <v>7307383</v>
+        <v>7307395</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4964,7 +4964,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4983,18 +4983,19 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5005,48 +5006,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135331144</v>
+        <v>135333369</v>
       </c>
       <c r="B41" t="n">
-        <v>83349</v>
+        <v>79452</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>492</v>
+        <v>864</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>623602</v>
+        <v>624013</v>
       </c>
       <c r="R41" t="n">
-        <v>7307395</v>
+        <v>7307360</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5075,7 +5076,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5085,7 +5086,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5094,19 +5095,18 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5117,32 +5117,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135333369</v>
+        <v>135333379</v>
       </c>
       <c r="B42" t="n">
-        <v>79452</v>
+        <v>92795</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>864</v>
+        <v>918</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5152,13 +5152,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>624013</v>
+        <v>624069</v>
       </c>
       <c r="R42" t="n">
-        <v>7307360</v>
+        <v>7307333</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5228,48 +5228,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135333379</v>
+        <v>135331034</v>
       </c>
       <c r="B43" t="n">
-        <v>92795</v>
+        <v>81355</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>918</v>
+        <v>1049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>624069</v>
+        <v>623627</v>
       </c>
       <c r="R43" t="n">
-        <v>7307333</v>
+        <v>7307253</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5296,19 +5296,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>16:47</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>16:47</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5323,12 +5313,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5339,10 +5329,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135331034</v>
+        <v>135331031</v>
       </c>
       <c r="B44" t="n">
-        <v>81355</v>
+        <v>91970</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5350,21 +5340,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1049</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5374,13 +5364,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>623627</v>
+        <v>623666</v>
       </c>
       <c r="R44" t="n">
-        <v>7307253</v>
+        <v>7307292</v>
       </c>
       <c r="S44" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5440,10 +5430,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135331031</v>
+        <v>135337861</v>
       </c>
       <c r="B45" t="n">
-        <v>91970</v>
+        <v>91974</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5451,34 +5441,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>623666</v>
+        <v>623609</v>
       </c>
       <c r="R45" t="n">
-        <v>7307292</v>
+        <v>7307443</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5508,29 +5498,45 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På tall över fuktigt vatten</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5541,10 +5547,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135337861</v>
+        <v>135331028</v>
       </c>
       <c r="B46" t="n">
-        <v>91974</v>
+        <v>83222</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5552,37 +5558,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>623609</v>
+        <v>623662</v>
       </c>
       <c r="R46" t="n">
-        <v>7307443</v>
+        <v>7307297</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5609,45 +5615,29 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På tall över fuktigt vatten</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5658,7 +5648,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135331028</v>
+        <v>135331037</v>
       </c>
       <c r="B47" t="n">
         <v>83222</v>
@@ -5693,13 +5683,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>623662</v>
+        <v>623600</v>
       </c>
       <c r="R47" t="n">
-        <v>7307297</v>
+        <v>7307269</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5759,7 +5749,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135331037</v>
+        <v>135332774</v>
       </c>
       <c r="B48" t="n">
         <v>83222</v>
@@ -5790,17 +5780,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>623600</v>
+        <v>623973</v>
       </c>
       <c r="R48" t="n">
-        <v>7307269</v>
+        <v>7307330</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5827,9 +5817,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5844,12 +5844,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5860,7 +5860,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135332774</v>
+        <v>135333363</v>
       </c>
       <c r="B49" t="n">
         <v>83222</v>
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>623973</v>
+        <v>624035</v>
       </c>
       <c r="R49" t="n">
-        <v>7307330</v>
+        <v>7307280</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5955,12 +5955,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5971,7 +5971,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135333363</v>
+        <v>135333367</v>
       </c>
       <c r="B50" t="n">
         <v>83222</v>
@@ -6006,13 +6006,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>624035</v>
+        <v>624036</v>
       </c>
       <c r="R50" t="n">
-        <v>7307280</v>
+        <v>7307333</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6082,7 +6082,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135333367</v>
+        <v>135333370</v>
       </c>
       <c r="B51" t="n">
         <v>83222</v>
@@ -6117,13 +6117,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>624036</v>
+        <v>624014</v>
       </c>
       <c r="R51" t="n">
-        <v>7307333</v>
+        <v>7307360</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6193,7 +6193,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135333370</v>
+        <v>135333377</v>
       </c>
       <c r="B52" t="n">
         <v>83222</v>
@@ -6228,13 +6228,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>624014</v>
+        <v>623784</v>
       </c>
       <c r="R52" t="n">
-        <v>7307360</v>
+        <v>7307352</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6304,10 +6304,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135333377</v>
+        <v>135331123</v>
       </c>
       <c r="B53" t="n">
-        <v>83222</v>
+        <v>91896</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6315,37 +6315,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>3242</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>623784</v>
+        <v>623681</v>
       </c>
       <c r="R53" t="n">
-        <v>7307352</v>
+        <v>7307293</v>
       </c>
       <c r="S53" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6399,12 +6399,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6415,48 +6415,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135331123</v>
+        <v>135332769</v>
       </c>
       <c r="B54" t="n">
-        <v>91896</v>
+        <v>91937</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3242</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>623681</v>
+        <v>624069</v>
       </c>
       <c r="R54" t="n">
-        <v>7307293</v>
+        <v>7307267</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6510,12 +6510,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6526,48 +6526,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135332769</v>
+        <v>135331027</v>
       </c>
       <c r="B55" t="n">
-        <v>91937</v>
+        <v>79373</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>624069</v>
+        <v>623680</v>
       </c>
       <c r="R55" t="n">
-        <v>7307267</v>
+        <v>7307293</v>
       </c>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6594,19 +6594,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6621,12 +6611,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6637,7 +6627,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135331027</v>
+        <v>135331029</v>
       </c>
       <c r="B56" t="n">
         <v>79373</v>
@@ -6672,13 +6662,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>623680</v>
+        <v>623660</v>
       </c>
       <c r="R56" t="n">
-        <v>7307293</v>
+        <v>7307297</v>
       </c>
       <c r="S56" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6738,7 +6728,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135331029</v>
+        <v>135331350</v>
       </c>
       <c r="B57" t="n">
         <v>79373</v>
@@ -6769,17 +6759,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>623660</v>
+        <v>623938</v>
       </c>
       <c r="R57" t="n">
-        <v>7307297</v>
+        <v>7307328</v>
       </c>
       <c r="S57" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6806,9 +6796,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6823,12 +6823,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6839,7 +6839,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135331350</v>
+        <v>135331670</v>
       </c>
       <c r="B58" t="n">
         <v>79373</v>
@@ -6870,17 +6870,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>623938</v>
+        <v>624012</v>
       </c>
       <c r="R58" t="n">
-        <v>7307328</v>
+        <v>7307326</v>
       </c>
       <c r="S58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6934,12 +6934,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6950,48 +6950,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135331670</v>
+        <v>135331033</v>
       </c>
       <c r="B59" t="n">
-        <v>79373</v>
+        <v>78776</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>624012</v>
+        <v>623649</v>
       </c>
       <c r="R59" t="n">
-        <v>7307326</v>
+        <v>7307278</v>
       </c>
       <c r="S59" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7018,19 +7018,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>15:47</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>15:47</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7045,12 +7035,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7061,7 +7051,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135331033</v>
+        <v>135333364</v>
       </c>
       <c r="B60" t="n">
         <v>78776</v>
@@ -7092,14 +7082,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>623649</v>
+        <v>624037</v>
       </c>
       <c r="R60" t="n">
-        <v>7307278</v>
+        <v>7307285</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7129,9 +7119,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7146,12 +7146,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7162,7 +7162,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135333364</v>
+        <v>135333375</v>
       </c>
       <c r="B61" t="n">
         <v>78776</v>
@@ -7197,13 +7197,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>624037</v>
+        <v>623832</v>
       </c>
       <c r="R61" t="n">
-        <v>7307285</v>
+        <v>7307315</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7273,7 +7273,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135333375</v>
+        <v>135358216</v>
       </c>
       <c r="B62" t="n">
         <v>78776</v>
@@ -7308,13 +7308,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>623832</v>
+        <v>624015</v>
       </c>
       <c r="R62" t="n">
-        <v>7307315</v>
+        <v>7307320</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7368,12 +7368,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7384,10 +7384,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135358216</v>
+        <v>135332772</v>
       </c>
       <c r="B63" t="n">
-        <v>78776</v>
+        <v>83358</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7395,21 +7395,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7419,13 +7419,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>624015</v>
+        <v>624017</v>
       </c>
       <c r="R63" t="n">
-        <v>7307320</v>
+        <v>7307324</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7479,12 +7479,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7495,7 +7495,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135332772</v>
+        <v>135332775</v>
       </c>
       <c r="B64" t="n">
         <v>83358</v>
@@ -7530,13 +7530,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>624017</v>
+        <v>623971</v>
       </c>
       <c r="R64" t="n">
-        <v>7307324</v>
+        <v>7307331</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7606,10 +7606,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135332775</v>
+        <v>135331035</v>
       </c>
       <c r="B65" t="n">
-        <v>83358</v>
+        <v>79992</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7617,37 +7617,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>623971</v>
+        <v>623629</v>
       </c>
       <c r="R65" t="n">
-        <v>7307331</v>
+        <v>7307251</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7674,19 +7674,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>16:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7701,12 +7691,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7717,7 +7707,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135331035</v>
+        <v>135332771</v>
       </c>
       <c r="B66" t="n">
         <v>79992</v>
@@ -7748,17 +7738,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>623629</v>
+        <v>624036</v>
       </c>
       <c r="R66" t="n">
-        <v>7307251</v>
+        <v>7307307</v>
       </c>
       <c r="S66" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7785,9 +7775,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7802,12 +7802,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7818,7 +7818,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135332771</v>
+        <v>135332776</v>
       </c>
       <c r="B67" t="n">
         <v>79992</v>
@@ -7853,13 +7853,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>624036</v>
+        <v>623926</v>
       </c>
       <c r="R67" t="n">
-        <v>7307307</v>
+        <v>7307301</v>
       </c>
       <c r="S67" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7929,7 +7929,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135332776</v>
+        <v>135333181</v>
       </c>
       <c r="B68" t="n">
         <v>79992</v>
@@ -7960,17 +7960,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>623926</v>
+        <v>623638</v>
       </c>
       <c r="R68" t="n">
-        <v>7307301</v>
+        <v>7307259</v>
       </c>
       <c r="S68" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8024,12 +8024,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8040,48 +8040,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135333181</v>
+        <v>135333371</v>
       </c>
       <c r="B69" t="n">
-        <v>79992</v>
+        <v>57972</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>623638</v>
+        <v>624014</v>
       </c>
       <c r="R69" t="n">
-        <v>7307259</v>
+        <v>7307360</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8135,12 +8135,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8151,7 +8151,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135333371</v>
+        <v>135333374</v>
       </c>
       <c r="B70" t="n">
         <v>57972</v>
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>624014</v>
+        <v>623919</v>
       </c>
       <c r="R70" t="n">
-        <v>7307360</v>
+        <v>7307361</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8221,7 +8221,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8231,7 +8231,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8262,27 +8267,27 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135333374</v>
+        <v>135318090</v>
       </c>
       <c r="B71" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8293,17 +8298,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>623919</v>
+        <v>623800</v>
       </c>
       <c r="R71" t="n">
-        <v>7307361</v>
+        <v>7307412</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8332,7 +8337,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8342,12 +8347,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8362,23 +8362,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135318090</v>
+        <v>135331038</v>
       </c>
       <c r="B72" t="n">
         <v>57975</v>
@@ -8409,17 +8405,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>623800</v>
+        <v>623589</v>
       </c>
       <c r="R72" t="n">
-        <v>7307412</v>
+        <v>7307264</v>
       </c>
       <c r="S72" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8446,19 +8442,14 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:12</t>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8473,19 +8464,23 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
+          <t>Helen Sterner</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135331038</v>
+        <v>135332777</v>
       </c>
       <c r="B73" t="n">
         <v>57975</v>
@@ -8514,19 +8509,24 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>623589</v>
+        <v>623904</v>
       </c>
       <c r="R73" t="n">
-        <v>7307264</v>
+        <v>7307334</v>
       </c>
       <c r="S73" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8553,14 +8553,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8575,12 +8580,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8591,7 +8596,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135332777</v>
+        <v>135332781</v>
       </c>
       <c r="B74" t="n">
         <v>57975</v>
@@ -8631,10 +8636,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>623904</v>
+        <v>623790</v>
       </c>
       <c r="R74" t="n">
-        <v>7307334</v>
+        <v>7307346</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8666,7 +8671,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8676,7 +8681,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8707,7 +8712,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135332781</v>
+        <v>135332783</v>
       </c>
       <c r="B75" t="n">
         <v>57975</v>
@@ -8736,24 +8741,19 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>623790</v>
+        <v>623971</v>
       </c>
       <c r="R75" t="n">
-        <v>7307346</v>
+        <v>7307384</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8792,14 +8792,19 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>skalade undertryckta granar, flera stycken</t>
         </is>
       </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG75" t="b">
         <v>0</v>
@@ -8823,7 +8828,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135332783</v>
+        <v>135332786</v>
       </c>
       <c r="B76" t="n">
         <v>57975</v>
@@ -8852,19 +8857,24 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>623971</v>
+        <v>624077</v>
       </c>
       <c r="R76" t="n">
-        <v>7307384</v>
+        <v>7307313</v>
       </c>
       <c r="S76" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8893,7 +8903,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8903,19 +8913,14 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>skalade undertryckta granar, flera stycken</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="b">
         <v>0</v>
@@ -8939,7 +8944,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135332786</v>
+        <v>135333182</v>
       </c>
       <c r="B77" t="n">
         <v>57975</v>
@@ -8968,24 +8973,19 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>624077</v>
+        <v>623602</v>
       </c>
       <c r="R77" t="n">
-        <v>7307313</v>
+        <v>7307284</v>
       </c>
       <c r="S77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9024,7 +9024,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9039,12 +9044,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9055,7 +9060,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135333182</v>
+        <v>135337852</v>
       </c>
       <c r="B78" t="n">
         <v>57975</v>
@@ -9086,14 +9091,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>623602</v>
+        <v>623747</v>
       </c>
       <c r="R78" t="n">
-        <v>7307284</v>
+        <v>7307427</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9125,7 +9130,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9135,12 +9140,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9155,12 +9160,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9171,45 +9176,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135337852</v>
+        <v>135331121</v>
       </c>
       <c r="B79" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>623747</v>
+        <v>623943</v>
       </c>
       <c r="R79" t="n">
-        <v>7307427</v>
+        <v>7307296</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9241,7 +9246,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9251,12 +9256,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:19</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9271,12 +9271,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9287,7 +9287,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135331121</v>
+        <v>135331122</v>
       </c>
       <c r="B80" t="n">
         <v>57162</v>
@@ -9322,10 +9322,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>623943</v>
+        <v>623926</v>
       </c>
       <c r="R80" t="n">
-        <v>7307296</v>
+        <v>7307337</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9357,7 +9357,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9367,7 +9367,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Tjäderbo? eller uppehallsplats?</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9398,10 +9403,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135331122</v>
+        <v>135331032</v>
       </c>
       <c r="B81" t="n">
-        <v>57162</v>
+        <v>5181</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9409,37 +9414,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>623926</v>
+        <v>623649</v>
       </c>
       <c r="R81" t="n">
-        <v>7307337</v>
+        <v>7307278</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9466,24 +9471,14 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Tjäderbo? eller uppehallsplats?</t>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9498,12 +9493,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9514,7 +9509,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135331032</v>
+        <v>135333376</v>
       </c>
       <c r="B82" t="n">
         <v>5181</v>
@@ -9545,17 +9540,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>623649</v>
+        <v>623799</v>
       </c>
       <c r="R82" t="n">
-        <v>7307278</v>
+        <v>7307327</v>
       </c>
       <c r="S82" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9582,9 +9577,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -9604,12 +9609,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9620,32 +9625,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135333376</v>
+        <v>135332770</v>
       </c>
       <c r="B83" t="n">
-        <v>5181</v>
+        <v>58136</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9655,13 +9660,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>623799</v>
+        <v>624031</v>
       </c>
       <c r="R83" t="n">
-        <v>7307327</v>
+        <v>7307306</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9690,7 +9695,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9700,12 +9705,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Gnag</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9720,12 +9720,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9736,7 +9736,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135332770</v>
+        <v>135333365</v>
       </c>
       <c r="B84" t="n">
         <v>58136</v>
@@ -9771,13 +9771,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>624031</v>
+        <v>624039</v>
       </c>
       <c r="R84" t="n">
-        <v>7307306</v>
+        <v>7307316</v>
       </c>
       <c r="S84" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9831,12 +9831,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9847,7 +9847,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135333365</v>
+        <v>135333378</v>
       </c>
       <c r="B85" t="n">
         <v>58136</v>
@@ -9882,13 +9882,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>624039</v>
+        <v>624079</v>
       </c>
       <c r="R85" t="n">
-        <v>7307316</v>
+        <v>7307360</v>
       </c>
       <c r="S85" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9927,7 +9927,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Familjegrupp, minst 5 st</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9958,48 +9963,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135333378</v>
+        <v>135331030</v>
       </c>
       <c r="B86" t="n">
-        <v>58136</v>
+        <v>5201</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>103021</v>
+        <v>105930</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>624079</v>
+        <v>623665</v>
       </c>
       <c r="R86" t="n">
-        <v>7307360</v>
+        <v>7307294</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10026,24 +10031,14 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>16:40</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>16:40</t>
-        </is>
-      </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Familjegrupp, minst 5 st</t>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10058,12 +10053,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -10074,10 +10069,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135331030</v>
+        <v>135333372</v>
       </c>
       <c r="B87" t="n">
-        <v>5201</v>
+        <v>99099</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10085,37 +10080,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>105930</v>
+        <v>220093</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>623665</v>
+        <v>624008</v>
       </c>
       <c r="R87" t="n">
-        <v>7307294</v>
+        <v>7307352</v>
       </c>
       <c r="S87" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10142,14 +10137,24 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Gnag</t>
+          <t>Kolla</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10164,12 +10169,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10180,10 +10185,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135333372</v>
+        <v>135331671</v>
       </c>
       <c r="B88" t="n">
-        <v>99099</v>
+        <v>98060</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10191,34 +10196,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220093</v>
+        <v>221945</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>624008</v>
+        <v>623997</v>
       </c>
       <c r="R88" t="n">
-        <v>7307352</v>
+        <v>7307348</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10250,7 +10255,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10260,12 +10265,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Kolla</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10280,12 +10280,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -10296,10 +10296,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135331671</v>
+        <v>135331145</v>
       </c>
       <c r="B89" t="n">
-        <v>98060</v>
+        <v>99217</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10307,37 +10307,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>623997</v>
+        <v>623644</v>
       </c>
       <c r="R89" t="n">
-        <v>7307348</v>
+        <v>7307354</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10391,12 +10391,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -10407,7 +10407,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135331145</v>
+        <v>135331672</v>
       </c>
       <c r="B90" t="n">
         <v>99217</v>
@@ -10438,17 +10438,17 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>623644</v>
+        <v>624001</v>
       </c>
       <c r="R90" t="n">
-        <v>7307354</v>
+        <v>7307352</v>
       </c>
       <c r="S90" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10502,12 +10502,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -10518,7 +10518,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135331672</v>
+        <v>135331673</v>
       </c>
       <c r="B91" t="n">
         <v>99217</v>
@@ -10553,13 +10553,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>624001</v>
+        <v>623969</v>
       </c>
       <c r="R91" t="n">
-        <v>7307352</v>
+        <v>7307338</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10629,7 +10629,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135331673</v>
+        <v>135331674</v>
       </c>
       <c r="B92" t="n">
         <v>99217</v>
@@ -10664,13 +10664,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>623969</v>
+        <v>623948</v>
       </c>
       <c r="R92" t="n">
-        <v>7307338</v>
+        <v>7307327</v>
       </c>
       <c r="S92" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10740,48 +10740,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135331674</v>
+        <v>135331039</v>
       </c>
       <c r="B93" t="n">
-        <v>99217</v>
+        <v>79963</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221952</v>
+        <v>229821</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>623948</v>
+        <v>623714</v>
       </c>
       <c r="R93" t="n">
-        <v>7307327</v>
+        <v>7307148</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10808,19 +10808,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>16:10</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10835,12 +10825,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10851,7 +10841,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135331039</v>
+        <v>135331124</v>
       </c>
       <c r="B94" t="n">
         <v>79963</v>
@@ -10882,17 +10872,17 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>623714</v>
+        <v>623675</v>
       </c>
       <c r="R94" t="n">
-        <v>7307148</v>
+        <v>7307271</v>
       </c>
       <c r="S94" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10919,9 +10909,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10936,12 +10936,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10952,7 +10952,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135331124</v>
+        <v>135331125</v>
       </c>
       <c r="B95" t="n">
         <v>79963</v>
@@ -10987,13 +10987,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>623675</v>
+        <v>623635</v>
       </c>
       <c r="R95" t="n">
-        <v>7307271</v>
+        <v>7307226</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11032,7 +11032,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Stubbe med yxhugg ser bild</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11063,10 +11068,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135331125</v>
+        <v>135331119</v>
       </c>
       <c r="B96" t="n">
-        <v>79963</v>
+        <v>79396</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11074,21 +11079,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>229821</v>
+        <v>260591</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11098,13 +11103,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>623635</v>
+        <v>624074</v>
       </c>
       <c r="R96" t="n">
-        <v>7307226</v>
+        <v>7307283</v>
       </c>
       <c r="S96" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11133,7 +11138,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11143,12 +11148,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Stubbe med yxhugg ser bild</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11157,6 +11157,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -11179,7 +11180,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135331119</v>
+        <v>135331669</v>
       </c>
       <c r="B97" t="n">
         <v>79396</v>
@@ -11210,17 +11211,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>624074</v>
+        <v>624037</v>
       </c>
       <c r="R97" t="n">
-        <v>7307283</v>
+        <v>7307291</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11249,7 +11250,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11259,7 +11260,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11268,19 +11269,18 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -11291,7 +11291,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135331669</v>
+        <v>135332778</v>
       </c>
       <c r="B98" t="n">
         <v>79396</v>
@@ -11322,17 +11322,17 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>624037</v>
+        <v>623849</v>
       </c>
       <c r="R98" t="n">
-        <v>7307291</v>
+        <v>7307318</v>
       </c>
       <c r="S98" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11386,12 +11386,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11402,7 +11402,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135332778</v>
+        <v>135333180</v>
       </c>
       <c r="B99" t="n">
         <v>79396</v>
@@ -11433,17 +11433,17 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>623849</v>
+        <v>623673</v>
       </c>
       <c r="R99" t="n">
-        <v>7307318</v>
+        <v>7307275</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11497,12 +11497,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11513,7 +11513,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135333180</v>
+        <v>135333382</v>
       </c>
       <c r="B100" t="n">
         <v>79396</v>
@@ -11544,17 +11544,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>623673</v>
+        <v>624084</v>
       </c>
       <c r="R100" t="n">
-        <v>7307275</v>
+        <v>7307323</v>
       </c>
       <c r="S100" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11608,126 +11608,15 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>135333382</v>
-      </c>
-      <c r="B101" t="n">
-        <v>79396</v>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>Tsågávvrie, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q101" t="n">
-        <v>624084</v>
-      </c>
-      <c r="R101" t="n">
-        <v>7307323</v>
-      </c>
-      <c r="S101" t="n">
-        <v>6</v>
-      </c>
-      <c r="T101" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W101" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y101" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AA101" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AD101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT101" t="inlineStr"/>
-      <c r="AW101" t="inlineStr">
-        <is>
-          <t>Linda Nordström</t>
-        </is>
-      </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>Linda Nordström</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY100"/>
+  <dimension ref="A1:AY101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2340,7 +2340,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135333184</v>
+        <v>135331130</v>
       </c>
       <c r="B17" t="n">
         <v>79373</v>
@@ -2369,19 +2369,22 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623581</v>
+        <v>623561</v>
       </c>
       <c r="R17" t="n">
-        <v>7307301</v>
+        <v>7307299</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2410,7 +2413,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2420,7 +2423,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2429,18 +2432,19 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2451,7 +2455,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135333188</v>
+        <v>135333184</v>
       </c>
       <c r="B18" t="n">
         <v>79373</v>
@@ -2486,13 +2490,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623541</v>
+        <v>623581</v>
       </c>
       <c r="R18" t="n">
-        <v>7307359</v>
+        <v>7307301</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2521,7 +2525,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2531,7 +2535,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2562,7 +2566,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135333190</v>
+        <v>135333188</v>
       </c>
       <c r="B19" t="n">
         <v>79373</v>
@@ -2597,10 +2601,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623521</v>
+        <v>623541</v>
       </c>
       <c r="R19" t="n">
-        <v>7307382</v>
+        <v>7307359</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2632,7 +2636,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,7 +2646,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2673,48 +2677,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135320009</v>
+        <v>135333190</v>
       </c>
       <c r="B20" t="n">
-        <v>78776</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623461</v>
+        <v>623521</v>
       </c>
       <c r="R20" t="n">
-        <v>7307589</v>
+        <v>7307382</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2743,7 +2747,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2753,7 +2757,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2768,22 +2772,26 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135333183</v>
+        <v>135320009</v>
       </c>
       <c r="B21" t="n">
-        <v>83358</v>
+        <v>78776</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2791,37 +2799,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623578</v>
+        <v>623461</v>
       </c>
       <c r="R21" t="n">
-        <v>7307305</v>
+        <v>7307589</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2850,7 +2858,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2860,7 +2868,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2875,26 +2883,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135319971</v>
+        <v>135333183</v>
       </c>
       <c r="B22" t="n">
-        <v>79992</v>
+        <v>83358</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2902,37 +2906,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623461</v>
+        <v>623578</v>
       </c>
       <c r="R22" t="n">
-        <v>7307589</v>
+        <v>7307305</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2961,7 +2965,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2971,7 +2975,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2986,19 +2990,23 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135333185</v>
+        <v>135319971</v>
       </c>
       <c r="B23" t="n">
         <v>79992</v>
@@ -3029,17 +3037,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>623521</v>
+        <v>623461</v>
       </c>
       <c r="R23" t="n">
-        <v>7307328</v>
+        <v>7307589</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3068,7 +3076,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3078,7 +3086,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3093,48 +3101,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135333191</v>
+        <v>135333185</v>
       </c>
       <c r="B24" t="n">
-        <v>80500</v>
+        <v>79992</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3144,13 +3148,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623500</v>
+        <v>623521</v>
       </c>
       <c r="R24" t="n">
-        <v>7307377</v>
+        <v>7307328</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3179,7 +3183,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3189,7 +3193,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3220,48 +3224,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135319479</v>
+        <v>135333191</v>
       </c>
       <c r="B25" t="n">
-        <v>57975</v>
+        <v>80500</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>623472</v>
+        <v>623500</v>
       </c>
       <c r="R25" t="n">
-        <v>7307510</v>
+        <v>7307377</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3290,7 +3294,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3300,12 +3304,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Spår</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3320,19 +3319,23 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135319812</v>
+        <v>135319479</v>
       </c>
       <c r="B26" t="n">
         <v>57975</v>
@@ -3367,10 +3370,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>623492</v>
+        <v>623472</v>
       </c>
       <c r="R26" t="n">
-        <v>7307534</v>
+        <v>7307510</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3402,7 +3405,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3412,7 +3415,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3444,7 +3447,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135320195</v>
+        <v>135319812</v>
       </c>
       <c r="B27" t="n">
         <v>57975</v>
@@ -3479,10 +3482,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>623500</v>
+        <v>623492</v>
       </c>
       <c r="R27" t="n">
-        <v>7307689</v>
+        <v>7307534</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3514,7 +3517,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3524,7 +3527,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3556,7 +3559,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135320511</v>
+        <v>135320195</v>
       </c>
       <c r="B28" t="n">
         <v>57975</v>
@@ -3591,10 +3594,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>623489</v>
+        <v>623500</v>
       </c>
       <c r="R28" t="n">
-        <v>7307496</v>
+        <v>7307689</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3626,7 +3629,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3636,12 +3639,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Gamla spår</t>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3668,7 +3671,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135337854</v>
+        <v>135320511</v>
       </c>
       <c r="B29" t="n">
         <v>57975</v>
@@ -3699,17 +3702,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>623570</v>
+        <v>623489</v>
       </c>
       <c r="R29" t="n">
-        <v>7307448</v>
+        <v>7307496</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3738,7 +3741,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3748,12 +3751,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Spår</t>
+          <t>Gamla spår</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3776,15 +3779,11 @@
           <t>Ulrika Karlsson</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135337855</v>
+        <v>135337854</v>
       </c>
       <c r="B30" t="n">
         <v>57975</v>
@@ -3819,10 +3818,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>623573</v>
+        <v>623570</v>
       </c>
       <c r="R30" t="n">
-        <v>7307467</v>
+        <v>7307448</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3854,7 +3853,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3864,7 +3863,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3900,7 +3899,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135337857</v>
+        <v>135337855</v>
       </c>
       <c r="B31" t="n">
         <v>57975</v>
@@ -3929,10 +3928,6 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
@@ -3942,7 +3937,7 @@
         <v>623573</v>
       </c>
       <c r="R31" t="n">
-        <v>7307487</v>
+        <v>7307467</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3974,7 +3969,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3984,12 +3979,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Spår på två träd</t>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4020,35 +4015,39 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135337862</v>
+        <v>135337857</v>
       </c>
       <c r="B32" t="n">
-        <v>106309</v>
+        <v>57975</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
@@ -4058,10 +4057,10 @@
         <v>623573</v>
       </c>
       <c r="R32" t="n">
-        <v>7307459</v>
+        <v>7307487</v>
       </c>
       <c r="S32" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4085,22 +4084,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Spår på två träd</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4131,10 +4135,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135319835</v>
+        <v>135337862</v>
       </c>
       <c r="B33" t="n">
-        <v>98060</v>
+        <v>106309</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4142,37 +4146,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>623492</v>
+        <v>623573</v>
       </c>
       <c r="R33" t="n">
-        <v>7307534</v>
+        <v>7307459</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4196,22 +4200,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4234,52 +4238,56 @@
           <t>Ulrika Karlsson</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135331126</v>
+        <v>135319835</v>
       </c>
       <c r="B34" t="n">
-        <v>79963</v>
+        <v>98060</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>623584</v>
+        <v>623492</v>
       </c>
       <c r="R34" t="n">
-        <v>7307249</v>
+        <v>7307534</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4308,7 +4316,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4318,7 +4326,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4333,23 +4341,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135331128</v>
+        <v>135331126</v>
       </c>
       <c r="B35" t="n">
         <v>79963</v>
@@ -4384,13 +4388,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>623566</v>
+        <v>623584</v>
       </c>
       <c r="R35" t="n">
-        <v>7307255</v>
+        <v>7307249</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4419,7 +4423,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4429,7 +4433,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4460,7 +4464,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135333186</v>
+        <v>135331128</v>
       </c>
       <c r="B36" t="n">
         <v>79963</v>
@@ -4491,14 +4495,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>623526</v>
+        <v>623566</v>
       </c>
       <c r="R36" t="n">
-        <v>7307330</v>
+        <v>7307255</v>
       </c>
       <c r="S36" t="n">
         <v>6</v>
@@ -4530,7 +4534,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4540,7 +4544,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4555,12 +4559,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4571,10 +4575,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135331143</v>
+        <v>135333186</v>
       </c>
       <c r="B37" t="n">
-        <v>83350</v>
+        <v>79963</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4582,37 +4586,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>308</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>623620</v>
+        <v>623526</v>
       </c>
       <c r="R37" t="n">
-        <v>7307390</v>
+        <v>7307330</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4641,7 +4645,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4651,7 +4655,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4666,12 +4670,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4682,10 +4686,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135331036</v>
+        <v>135331143</v>
       </c>
       <c r="B38" t="n">
-        <v>79039</v>
+        <v>83350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4693,37 +4697,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>623619</v>
+        <v>623620</v>
       </c>
       <c r="R38" t="n">
-        <v>7307249</v>
+        <v>7307390</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4750,9 +4754,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4767,12 +4781,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4783,7 +4797,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135332782</v>
+        <v>135331036</v>
       </c>
       <c r="B39" t="n">
         <v>79039</v>
@@ -4814,17 +4828,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>623828</v>
+        <v>623619</v>
       </c>
       <c r="R39" t="n">
-        <v>7307383</v>
+        <v>7307249</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4851,19 +4865,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>16:25</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4878,12 +4882,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4894,45 +4898,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135331144</v>
+        <v>135332782</v>
       </c>
       <c r="B40" t="n">
-        <v>83349</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>492</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>623602</v>
+        <v>623828</v>
       </c>
       <c r="R40" t="n">
-        <v>7307395</v>
+        <v>7307383</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4964,7 +4968,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4974,7 +4978,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4983,19 +4987,18 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5006,48 +5009,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135333369</v>
+        <v>135331144</v>
       </c>
       <c r="B41" t="n">
-        <v>79452</v>
+        <v>83349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>864</v>
+        <v>492</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>624013</v>
+        <v>623602</v>
       </c>
       <c r="R41" t="n">
-        <v>7307360</v>
+        <v>7307395</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5076,7 +5079,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5086,7 +5089,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5095,18 +5098,19 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5117,32 +5121,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135333379</v>
+        <v>135333369</v>
       </c>
       <c r="B42" t="n">
-        <v>92795</v>
+        <v>79452</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>918</v>
+        <v>864</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5152,13 +5156,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>624069</v>
+        <v>624013</v>
       </c>
       <c r="R42" t="n">
-        <v>7307333</v>
+        <v>7307360</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5187,7 +5191,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5197,7 +5201,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5228,48 +5232,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135331034</v>
+        <v>135333379</v>
       </c>
       <c r="B43" t="n">
-        <v>81355</v>
+        <v>92795</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1049</v>
+        <v>918</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>623627</v>
+        <v>624069</v>
       </c>
       <c r="R43" t="n">
-        <v>7307253</v>
+        <v>7307333</v>
       </c>
       <c r="S43" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5296,9 +5300,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5313,12 +5327,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5329,10 +5343,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135331031</v>
+        <v>135331034</v>
       </c>
       <c r="B44" t="n">
-        <v>91970</v>
+        <v>81355</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5340,21 +5354,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>1049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5364,13 +5378,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>623666</v>
+        <v>623627</v>
       </c>
       <c r="R44" t="n">
-        <v>7307292</v>
+        <v>7307253</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5430,10 +5444,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135337861</v>
+        <v>135331031</v>
       </c>
       <c r="B45" t="n">
-        <v>91974</v>
+        <v>91970</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5441,34 +5455,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>623609</v>
+        <v>623666</v>
       </c>
       <c r="R45" t="n">
-        <v>7307443</v>
+        <v>7307292</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5498,45 +5512,29 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På tall över fuktigt vatten</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5547,10 +5545,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135331028</v>
+        <v>135337861</v>
       </c>
       <c r="B46" t="n">
-        <v>83222</v>
+        <v>91974</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5558,37 +5556,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>623662</v>
+        <v>623609</v>
       </c>
       <c r="R46" t="n">
-        <v>7307297</v>
+        <v>7307443</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5615,29 +5613,45 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På tall över fuktigt vatten</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5648,7 +5662,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135331037</v>
+        <v>135331028</v>
       </c>
       <c r="B47" t="n">
         <v>83222</v>
@@ -5683,13 +5697,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>623600</v>
+        <v>623662</v>
       </c>
       <c r="R47" t="n">
-        <v>7307269</v>
+        <v>7307297</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5749,7 +5763,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135332774</v>
+        <v>135331037</v>
       </c>
       <c r="B48" t="n">
         <v>83222</v>
@@ -5780,17 +5794,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>623973</v>
+        <v>623600</v>
       </c>
       <c r="R48" t="n">
-        <v>7307330</v>
+        <v>7307269</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5817,19 +5831,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>15:57</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5844,12 +5848,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5860,7 +5864,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135333363</v>
+        <v>135332774</v>
       </c>
       <c r="B49" t="n">
         <v>83222</v>
@@ -5895,13 +5899,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>624035</v>
+        <v>623973</v>
       </c>
       <c r="R49" t="n">
-        <v>7307280</v>
+        <v>7307330</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5930,7 +5934,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5940,7 +5944,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5955,12 +5959,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5971,7 +5975,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135333367</v>
+        <v>135333363</v>
       </c>
       <c r="B50" t="n">
         <v>83222</v>
@@ -6006,13 +6010,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>624036</v>
+        <v>624035</v>
       </c>
       <c r="R50" t="n">
-        <v>7307333</v>
+        <v>7307280</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6041,7 +6045,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6051,7 +6055,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6082,7 +6086,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135333370</v>
+        <v>135333367</v>
       </c>
       <c r="B51" t="n">
         <v>83222</v>
@@ -6117,13 +6121,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>624014</v>
+        <v>624036</v>
       </c>
       <c r="R51" t="n">
-        <v>7307360</v>
+        <v>7307333</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6152,7 +6156,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6162,7 +6166,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6193,7 +6197,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135333377</v>
+        <v>135333370</v>
       </c>
       <c r="B52" t="n">
         <v>83222</v>
@@ -6228,13 +6232,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>623784</v>
+        <v>624014</v>
       </c>
       <c r="R52" t="n">
-        <v>7307352</v>
+        <v>7307360</v>
       </c>
       <c r="S52" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6263,7 +6267,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6273,7 +6277,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6304,10 +6308,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135331123</v>
+        <v>135333377</v>
       </c>
       <c r="B53" t="n">
-        <v>91896</v>
+        <v>83222</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6315,37 +6319,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3242</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>623681</v>
+        <v>623784</v>
       </c>
       <c r="R53" t="n">
-        <v>7307293</v>
+        <v>7307352</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6374,7 +6378,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6384,7 +6388,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6399,12 +6403,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6415,48 +6419,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135332769</v>
+        <v>135331123</v>
       </c>
       <c r="B54" t="n">
-        <v>91937</v>
+        <v>91896</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>3242</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>624069</v>
+        <v>623681</v>
       </c>
       <c r="R54" t="n">
-        <v>7307267</v>
+        <v>7307293</v>
       </c>
       <c r="S54" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6485,7 +6489,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6495,7 +6499,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6510,12 +6514,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6526,48 +6530,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135331027</v>
+        <v>135332769</v>
       </c>
       <c r="B55" t="n">
-        <v>79373</v>
+        <v>91937</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>623680</v>
+        <v>624069</v>
       </c>
       <c r="R55" t="n">
-        <v>7307293</v>
+        <v>7307267</v>
       </c>
       <c r="S55" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6594,9 +6598,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6611,12 +6625,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6627,7 +6641,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135331029</v>
+        <v>135331027</v>
       </c>
       <c r="B56" t="n">
         <v>79373</v>
@@ -6662,13 +6676,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>623660</v>
+        <v>623680</v>
       </c>
       <c r="R56" t="n">
-        <v>7307297</v>
+        <v>7307293</v>
       </c>
       <c r="S56" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6728,7 +6742,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135331350</v>
+        <v>135331029</v>
       </c>
       <c r="B57" t="n">
         <v>79373</v>
@@ -6759,17 +6773,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>623938</v>
+        <v>623660</v>
       </c>
       <c r="R57" t="n">
-        <v>7307328</v>
+        <v>7307297</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6796,19 +6810,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>16:12</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6823,12 +6827,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6839,7 +6843,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135331670</v>
+        <v>135331350</v>
       </c>
       <c r="B58" t="n">
         <v>79373</v>
@@ -6870,17 +6874,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>624012</v>
+        <v>623938</v>
       </c>
       <c r="R58" t="n">
-        <v>7307326</v>
+        <v>7307328</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6909,7 +6913,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6919,7 +6923,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6934,12 +6938,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6950,48 +6954,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135331033</v>
+        <v>135331670</v>
       </c>
       <c r="B59" t="n">
-        <v>78776</v>
+        <v>79373</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>623649</v>
+        <v>624012</v>
       </c>
       <c r="R59" t="n">
-        <v>7307278</v>
+        <v>7307326</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7018,9 +7022,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7035,12 +7049,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7051,7 +7065,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135333364</v>
+        <v>135331033</v>
       </c>
       <c r="B60" t="n">
         <v>78776</v>
@@ -7082,14 +7096,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>624037</v>
+        <v>623649</v>
       </c>
       <c r="R60" t="n">
-        <v>7307285</v>
+        <v>7307278</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7119,19 +7133,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>15:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7146,12 +7150,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7162,7 +7166,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135333375</v>
+        <v>135333364</v>
       </c>
       <c r="B61" t="n">
         <v>78776</v>
@@ -7197,13 +7201,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>623832</v>
+        <v>624037</v>
       </c>
       <c r="R61" t="n">
-        <v>7307315</v>
+        <v>7307285</v>
       </c>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7232,7 +7236,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7242,7 +7246,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7273,7 +7277,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135358216</v>
+        <v>135333375</v>
       </c>
       <c r="B62" t="n">
         <v>78776</v>
@@ -7308,13 +7312,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>624015</v>
+        <v>623832</v>
       </c>
       <c r="R62" t="n">
-        <v>7307320</v>
+        <v>7307315</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7343,7 +7347,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7353,7 +7357,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7368,12 +7372,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7384,10 +7388,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135332772</v>
+        <v>135358216</v>
       </c>
       <c r="B63" t="n">
-        <v>83358</v>
+        <v>78776</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7395,21 +7399,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7419,13 +7423,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>624017</v>
+        <v>624015</v>
       </c>
       <c r="R63" t="n">
-        <v>7307324</v>
+        <v>7307320</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7454,7 +7458,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7464,7 +7468,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7479,12 +7483,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7495,7 +7499,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135332775</v>
+        <v>135332772</v>
       </c>
       <c r="B64" t="n">
         <v>83358</v>
@@ -7530,13 +7534,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>623971</v>
+        <v>624017</v>
       </c>
       <c r="R64" t="n">
-        <v>7307331</v>
+        <v>7307324</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7565,7 +7569,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7575,7 +7579,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7606,10 +7610,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135331035</v>
+        <v>135332775</v>
       </c>
       <c r="B65" t="n">
-        <v>79992</v>
+        <v>83358</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7617,37 +7621,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>623629</v>
+        <v>623971</v>
       </c>
       <c r="R65" t="n">
-        <v>7307251</v>
+        <v>7307331</v>
       </c>
       <c r="S65" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7674,9 +7678,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7691,12 +7705,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7707,7 +7721,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135332771</v>
+        <v>135331035</v>
       </c>
       <c r="B66" t="n">
         <v>79992</v>
@@ -7738,17 +7752,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>624036</v>
+        <v>623629</v>
       </c>
       <c r="R66" t="n">
-        <v>7307307</v>
+        <v>7307251</v>
       </c>
       <c r="S66" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7775,19 +7789,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:44</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7802,12 +7806,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7818,7 +7822,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135332776</v>
+        <v>135332771</v>
       </c>
       <c r="B67" t="n">
         <v>79992</v>
@@ -7853,13 +7857,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>623926</v>
+        <v>624036</v>
       </c>
       <c r="R67" t="n">
-        <v>7307301</v>
+        <v>7307307</v>
       </c>
       <c r="S67" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7888,7 +7892,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7898,7 +7902,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7929,7 +7933,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135333181</v>
+        <v>135332776</v>
       </c>
       <c r="B68" t="n">
         <v>79992</v>
@@ -7960,17 +7964,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>623638</v>
+        <v>623926</v>
       </c>
       <c r="R68" t="n">
-        <v>7307259</v>
+        <v>7307301</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7999,7 +8003,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8009,7 +8013,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8024,12 +8028,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8040,48 +8044,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135333371</v>
+        <v>135333181</v>
       </c>
       <c r="B69" t="n">
-        <v>57972</v>
+        <v>79992</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>624014</v>
+        <v>623638</v>
       </c>
       <c r="R69" t="n">
-        <v>7307360</v>
+        <v>7307259</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8110,7 +8114,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8120,7 +8124,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8135,12 +8139,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8151,7 +8155,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135333374</v>
+        <v>135333371</v>
       </c>
       <c r="B70" t="n">
         <v>57972</v>
@@ -8186,10 +8190,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>623919</v>
+        <v>624014</v>
       </c>
       <c r="R70" t="n">
-        <v>7307361</v>
+        <v>7307360</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8221,7 +8225,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8231,12 +8235,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8267,27 +8266,27 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135318090</v>
+        <v>135333374</v>
       </c>
       <c r="B71" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8298,17 +8297,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Grundträsk, Grundträsk, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>623800</v>
+        <v>623919</v>
       </c>
       <c r="R71" t="n">
-        <v>7307412</v>
+        <v>7307361</v>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8337,7 +8336,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8347,7 +8346,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8362,19 +8366,23 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135331038</v>
+        <v>135318090</v>
       </c>
       <c r="B72" t="n">
         <v>57975</v>
@@ -8405,17 +8413,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Grundträsk, Grundträsk, Pi lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>623589</v>
+        <v>623800</v>
       </c>
       <c r="R72" t="n">
-        <v>7307264</v>
+        <v>7307412</v>
       </c>
       <c r="S72" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8442,14 +8450,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8464,23 +8477,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135332777</v>
+        <v>135331038</v>
       </c>
       <c r="B73" t="n">
         <v>57975</v>
@@ -8509,24 +8518,19 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>623904</v>
+        <v>623589</v>
       </c>
       <c r="R73" t="n">
-        <v>7307334</v>
+        <v>7307264</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8553,19 +8557,14 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>16:10</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8580,12 +8579,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8596,7 +8595,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135332781</v>
+        <v>135332777</v>
       </c>
       <c r="B74" t="n">
         <v>57975</v>
@@ -8636,10 +8635,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>623790</v>
+        <v>623904</v>
       </c>
       <c r="R74" t="n">
-        <v>7307346</v>
+        <v>7307334</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8671,7 +8670,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8681,7 +8680,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8712,7 +8711,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135332783</v>
+        <v>135332781</v>
       </c>
       <c r="B75" t="n">
         <v>57975</v>
@@ -8741,19 +8740,24 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>623971</v>
+        <v>623790</v>
       </c>
       <c r="R75" t="n">
-        <v>7307384</v>
+        <v>7307346</v>
       </c>
       <c r="S75" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8782,7 +8786,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8792,19 +8796,14 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:36</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>skalade undertryckta granar, flera stycken</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="b">
         <v>0</v>
@@ -8828,7 +8827,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135332786</v>
+        <v>135332783</v>
       </c>
       <c r="B76" t="n">
         <v>57975</v>
@@ -8857,24 +8856,19 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>624077</v>
+        <v>623971</v>
       </c>
       <c r="R76" t="n">
-        <v>7307313</v>
+        <v>7307384</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8903,7 +8897,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8913,14 +8907,19 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>skalade undertryckta granar, flera stycken</t>
         </is>
       </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG76" t="b">
         <v>0</v>
@@ -8944,7 +8943,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135333182</v>
+        <v>135332786</v>
       </c>
       <c r="B77" t="n">
         <v>57975</v>
@@ -8973,19 +8972,24 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>623602</v>
+        <v>624077</v>
       </c>
       <c r="R77" t="n">
-        <v>7307284</v>
+        <v>7307313</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9014,7 +9018,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9024,12 +9028,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9044,12 +9043,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9060,7 +9059,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135337852</v>
+        <v>135333182</v>
       </c>
       <c r="B78" t="n">
         <v>57975</v>
@@ -9091,14 +9090,14 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>623747</v>
+        <v>623602</v>
       </c>
       <c r="R78" t="n">
-        <v>7307427</v>
+        <v>7307284</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9130,7 +9129,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9140,12 +9139,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9160,12 +9159,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9176,45 +9175,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135331121</v>
+        <v>135337852</v>
       </c>
       <c r="B79" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>623943</v>
+        <v>623747</v>
       </c>
       <c r="R79" t="n">
-        <v>7307296</v>
+        <v>7307427</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9246,7 +9245,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9256,7 +9255,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9271,12 +9275,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9287,7 +9291,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135331122</v>
+        <v>135331121</v>
       </c>
       <c r="B80" t="n">
         <v>57162</v>
@@ -9322,10 +9326,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>623926</v>
+        <v>623943</v>
       </c>
       <c r="R80" t="n">
-        <v>7307337</v>
+        <v>7307296</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9357,7 +9361,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9367,12 +9371,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Tjäderbo? eller uppehallsplats?</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9403,10 +9402,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135331032</v>
+        <v>135331122</v>
       </c>
       <c r="B81" t="n">
-        <v>5181</v>
+        <v>57162</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9414,37 +9413,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>623649</v>
+        <v>623926</v>
       </c>
       <c r="R81" t="n">
-        <v>7307278</v>
+        <v>7307337</v>
       </c>
       <c r="S81" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9471,14 +9470,24 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Gnag</t>
+          <t>Tjäderbo? eller uppehallsplats?</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9493,12 +9502,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9509,7 +9518,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135333376</v>
+        <v>135331032</v>
       </c>
       <c r="B82" t="n">
         <v>5181</v>
@@ -9540,17 +9549,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>623799</v>
+        <v>623649</v>
       </c>
       <c r="R82" t="n">
-        <v>7307327</v>
+        <v>7307278</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9577,19 +9586,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>16:20</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -9609,12 +9608,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9625,32 +9624,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135332770</v>
+        <v>135333376</v>
       </c>
       <c r="B83" t="n">
-        <v>58136</v>
+        <v>5181</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9660,13 +9659,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>624031</v>
+        <v>623799</v>
       </c>
       <c r="R83" t="n">
-        <v>7307306</v>
+        <v>7307327</v>
       </c>
       <c r="S83" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9695,7 +9694,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9705,7 +9704,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9720,12 +9724,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9736,7 +9740,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135333365</v>
+        <v>135332770</v>
       </c>
       <c r="B84" t="n">
         <v>58136</v>
@@ -9771,13 +9775,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>624039</v>
+        <v>624031</v>
       </c>
       <c r="R84" t="n">
-        <v>7307316</v>
+        <v>7307306</v>
       </c>
       <c r="S84" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9806,7 +9810,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9816,7 +9820,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9831,12 +9835,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9847,7 +9851,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135333378</v>
+        <v>135333365</v>
       </c>
       <c r="B85" t="n">
         <v>58136</v>
@@ -9882,13 +9886,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>624079</v>
+        <v>624039</v>
       </c>
       <c r="R85" t="n">
-        <v>7307360</v>
+        <v>7307316</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9917,7 +9921,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9927,12 +9931,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Familjegrupp, minst 5 st</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9963,48 +9962,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135331030</v>
+        <v>135333378</v>
       </c>
       <c r="B86" t="n">
-        <v>5201</v>
+        <v>58136</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>623665</v>
+        <v>624079</v>
       </c>
       <c r="R86" t="n">
-        <v>7307294</v>
+        <v>7307360</v>
       </c>
       <c r="S86" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10031,14 +10030,24 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Gnag</t>
+          <t>Familjegrupp, minst 5 st</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10053,12 +10062,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -10069,10 +10078,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135333372</v>
+        <v>135331030</v>
       </c>
       <c r="B87" t="n">
-        <v>99099</v>
+        <v>5201</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10080,37 +10089,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220093</v>
+        <v>105930</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>624008</v>
+        <v>623665</v>
       </c>
       <c r="R87" t="n">
-        <v>7307352</v>
+        <v>7307294</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10137,24 +10146,14 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Kolla</t>
+          <t>Gnag</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10169,12 +10168,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10185,10 +10184,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135331671</v>
+        <v>135333372</v>
       </c>
       <c r="B88" t="n">
-        <v>98060</v>
+        <v>99099</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10196,34 +10195,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221945</v>
+        <v>220093</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>623997</v>
+        <v>624008</v>
       </c>
       <c r="R88" t="n">
-        <v>7307348</v>
+        <v>7307352</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10255,7 +10254,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10265,7 +10264,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Kolla</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10280,12 +10284,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -10296,10 +10300,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135331145</v>
+        <v>135331671</v>
       </c>
       <c r="B89" t="n">
-        <v>99217</v>
+        <v>98060</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10307,37 +10311,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>623644</v>
+        <v>623997</v>
       </c>
       <c r="R89" t="n">
-        <v>7307354</v>
+        <v>7307348</v>
       </c>
       <c r="S89" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10366,7 +10370,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10376,7 +10380,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10391,12 +10395,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -10407,7 +10411,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135331672</v>
+        <v>135331145</v>
       </c>
       <c r="B90" t="n">
         <v>99217</v>
@@ -10438,17 +10442,17 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>624001</v>
+        <v>623644</v>
       </c>
       <c r="R90" t="n">
-        <v>7307352</v>
+        <v>7307354</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10477,7 +10481,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10487,7 +10491,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10502,12 +10506,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -10518,7 +10522,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135331673</v>
+        <v>135331672</v>
       </c>
       <c r="B91" t="n">
         <v>99217</v>
@@ -10553,13 +10557,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>623969</v>
+        <v>624001</v>
       </c>
       <c r="R91" t="n">
-        <v>7307338</v>
+        <v>7307352</v>
       </c>
       <c r="S91" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10588,7 +10592,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10598,7 +10602,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10629,7 +10633,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135331674</v>
+        <v>135331673</v>
       </c>
       <c r="B92" t="n">
         <v>99217</v>
@@ -10664,13 +10668,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>623948</v>
+        <v>623969</v>
       </c>
       <c r="R92" t="n">
-        <v>7307327</v>
+        <v>7307338</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10699,7 +10703,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10709,7 +10713,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10740,48 +10744,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135331039</v>
+        <v>135331674</v>
       </c>
       <c r="B93" t="n">
-        <v>79963</v>
+        <v>99217</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Nära Änganäs, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>623714</v>
+        <v>623948</v>
       </c>
       <c r="R93" t="n">
-        <v>7307148</v>
+        <v>7307327</v>
       </c>
       <c r="S93" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10808,9 +10812,19 @@
           <t>2026-07-22</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10825,12 +10839,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Helen Sterner</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10841,7 +10855,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135331124</v>
+        <v>135331039</v>
       </c>
       <c r="B94" t="n">
         <v>79963</v>
@@ -10872,17 +10886,17 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
+          <t>Nära Änganäs, Pi lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>623675</v>
+        <v>623714</v>
       </c>
       <c r="R94" t="n">
-        <v>7307271</v>
+        <v>7307148</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10909,19 +10923,9 @@
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10936,12 +10940,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Helen Sterner</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10952,7 +10956,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135331125</v>
+        <v>135331124</v>
       </c>
       <c r="B95" t="n">
         <v>79963</v>
@@ -10987,13 +10991,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>623635</v>
+        <v>623675</v>
       </c>
       <c r="R95" t="n">
-        <v>7307226</v>
+        <v>7307271</v>
       </c>
       <c r="S95" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11022,7 +11026,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11032,12 +11036,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Stubbe med yxhugg ser bild</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11068,10 +11067,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135331119</v>
+        <v>135331125</v>
       </c>
       <c r="B96" t="n">
-        <v>79396</v>
+        <v>79963</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11079,21 +11078,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11103,13 +11102,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>624074</v>
+        <v>623635</v>
       </c>
       <c r="R96" t="n">
-        <v>7307283</v>
+        <v>7307226</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11138,7 +11137,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11148,7 +11147,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Stubbe med yxhugg ser bild</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11157,7 +11161,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -11180,7 +11183,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135331669</v>
+        <v>135331119</v>
       </c>
       <c r="B97" t="n">
         <v>79396</v>
@@ -11211,17 +11214,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>624037</v>
+        <v>624074</v>
       </c>
       <c r="R97" t="n">
-        <v>7307291</v>
+        <v>7307283</v>
       </c>
       <c r="S97" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11250,7 +11253,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11260,7 +11263,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11269,18 +11272,19 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -11291,7 +11295,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135332778</v>
+        <v>135331669</v>
       </c>
       <c r="B98" t="n">
         <v>79396</v>
@@ -11322,17 +11326,17 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>623849</v>
+        <v>624037</v>
       </c>
       <c r="R98" t="n">
-        <v>7307318</v>
+        <v>7307291</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11361,7 +11365,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11371,7 +11375,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11386,12 +11390,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11402,7 +11406,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135333180</v>
+        <v>135332778</v>
       </c>
       <c r="B99" t="n">
         <v>79396</v>
@@ -11433,17 +11437,17 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
+          <t>Tsågávvrie, Pi lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>623673</v>
+        <v>623849</v>
       </c>
       <c r="R99" t="n">
-        <v>7307275</v>
+        <v>7307318</v>
       </c>
       <c r="S99" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11472,7 +11476,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11482,7 +11486,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11497,12 +11501,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11513,7 +11517,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135333382</v>
+        <v>135333180</v>
       </c>
       <c r="B100" t="n">
         <v>79396</v>
@@ -11544,17 +11548,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Tsågávvrie, Pi lm</t>
+          <t>Ons Gr 2_Tsågávvrie_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>624084</v>
+        <v>623673</v>
       </c>
       <c r="R100" t="n">
-        <v>7307323</v>
+        <v>7307275</v>
       </c>
       <c r="S100" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11583,7 +11587,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11593,7 +11597,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11608,15 +11612,126 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>135333382</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Tsågávvrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>624084</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7307323</v>
+      </c>
+      <c r="S101" t="n">
+        <v>6</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
           <t>Linda Nordström</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
+      <c r="AX101" t="inlineStr">
         <is>
           <t>Linda Nordström</t>
         </is>
       </c>
-      <c r="AY100" t="inlineStr">
+      <c r="AY101" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
@@ -2271,7 +2271,7 @@
         <v>623499</v>
       </c>
       <c r="R16" t="n">
-        <v>7307487</v>
+        <v>7307488</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>

--- a/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
@@ -2271,7 +2271,7 @@
         <v>623499</v>
       </c>
       <c r="R16" t="n">
-        <v>7307488</v>
+        <v>7307487</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>

--- a/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY101"/>
+  <dimension ref="A1:AZ101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331137</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331133</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331136</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333192</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1233,6 +1258,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333193</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1350,6 +1380,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135337856</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1461,6 +1496,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333195</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1572,6 +1612,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331141</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1683,6 +1728,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331135</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1794,6 +1844,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331140</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1905,6 +1960,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331131</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2016,6 +2076,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331132</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2123,6 +2188,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320627</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2230,6 +2300,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135319473</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2337,6 +2412,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135319562</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2452,6 +2532,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331130</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2563,6 +2648,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333184</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2674,6 +2764,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333188</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2785,6 +2880,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333190</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2892,6 +2992,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320009</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3003,6 +3108,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333183</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3110,6 +3220,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135319971</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3221,6 +3336,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333185</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3332,6 +3452,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333191</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3444,6 +3569,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135319479</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3556,6 +3686,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135319812</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3668,6 +3803,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320195</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3780,6 +3920,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135320511</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3896,6 +4041,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135337854</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4010,6 +4160,11 @@
       <c r="AY31" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135337855</t>
         </is>
       </c>
     </row>
@@ -4132,6 +4287,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135337857</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4243,6 +4403,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135337862</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4350,6 +4515,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135319835</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4461,6 +4631,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331126</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4572,6 +4747,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331128</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4683,6 +4863,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333186</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4794,6 +4979,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331143</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4895,6 +5085,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331036</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5006,6 +5201,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332782</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5118,6 +5318,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331144</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5229,6 +5434,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333369</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5340,6 +5550,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333379</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5441,6 +5656,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331034</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5542,6 +5762,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331031</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5659,6 +5884,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135337861</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5760,6 +5990,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331028</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5861,6 +6096,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331037</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5972,6 +6212,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332774</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6083,6 +6328,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333363</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6194,6 +6444,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333367</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6305,6 +6560,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333370</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6416,6 +6676,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333377</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6527,6 +6792,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331123</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6638,6 +6908,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332769</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6739,6 +7014,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331027</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6840,6 +7120,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331029</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6951,6 +7236,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331350</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7062,6 +7352,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331670</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7163,6 +7458,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331033</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7274,6 +7574,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333364</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7385,6 +7690,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333375</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7496,6 +7806,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358216</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7607,6 +7922,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332772</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7718,6 +8038,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332775</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7819,6 +8144,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331035</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7930,6 +8260,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332771</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8041,6 +8376,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332776</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8152,6 +8492,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333181</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8263,6 +8608,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333371</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8379,6 +8729,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333374</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8486,6 +8841,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135318090</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8592,6 +8952,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331038</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8708,6 +9073,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332777</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8824,6 +9194,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332781</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8940,6 +9315,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332783</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9056,6 +9436,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332786</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9172,6 +9557,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333182</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9288,6 +9678,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135337852</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9399,6 +9794,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331121</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9515,6 +9915,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331122</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9621,6 +10026,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331032</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9737,6 +10147,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333376</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9848,6 +10263,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332770</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9959,6 +10379,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333365</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10075,6 +10500,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333378</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10181,6 +10611,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331030</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10297,6 +10732,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333372</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10408,6 +10848,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331671</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10519,6 +10964,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331145</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10630,6 +11080,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331672</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10741,6 +11196,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331673</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10852,6 +11312,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331674</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10953,6 +11418,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331039</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11064,6 +11534,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331124</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11180,6 +11655,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331125</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11292,6 +11772,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331119</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11403,6 +11888,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331669</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11514,6 +12004,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135332778</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11625,6 +12120,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333180</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11736,8 +12236,115 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333382</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
@@ -2346,7 +2346,7 @@
         <v>623499</v>
       </c>
       <c r="R16" t="n">
-        <v>7307488</v>
+        <v>7307487</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>

--- a/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
@@ -2346,7 +2346,7 @@
         <v>623499</v>
       </c>
       <c r="R16" t="n">
-        <v>7307487</v>
+        <v>7307488</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>

--- a/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135331137</v>
       </c>
       <c r="B2" t="n">
-        <v>83343</v>
+        <v>83383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>135331133</v>
       </c>
       <c r="B3" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>135331136</v>
       </c>
       <c r="B4" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>135333192</v>
       </c>
       <c r="B5" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>135333193</v>
       </c>
       <c r="B6" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>135337856</v>
       </c>
       <c r="B7" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>135333195</v>
       </c>
       <c r="B8" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>135331141</v>
       </c>
       <c r="B9" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>135331135</v>
       </c>
       <c r="B10" t="n">
-        <v>92167</v>
+        <v>92209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>135331140</v>
       </c>
       <c r="B11" t="n">
-        <v>92167</v>
+        <v>92209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>135331131</v>
       </c>
       <c r="B12" t="n">
-        <v>96678</v>
+        <v>96722</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>135331132</v>
       </c>
       <c r="B13" t="n">
-        <v>97308</v>
+        <v>97352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>135320627</v>
       </c>
       <c r="B14" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>135319473</v>
       </c>
       <c r="B15" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>135319562</v>
       </c>
       <c r="B16" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>135331130</v>
       </c>
       <c r="B17" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>135333184</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>135333188</v>
       </c>
       <c r="B19" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>135333190</v>
       </c>
       <c r="B20" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>135320009</v>
       </c>
       <c r="B21" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>135333183</v>
       </c>
       <c r="B22" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>135319971</v>
       </c>
       <c r="B23" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>135333185</v>
       </c>
       <c r="B24" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>135333191</v>
       </c>
       <c r="B25" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>135319479</v>
       </c>
       <c r="B26" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>135319812</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>135320195</v>
       </c>
       <c r="B28" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>135320511</v>
       </c>
       <c r="B29" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>135337854</v>
       </c>
       <c r="B30" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>135337855</v>
       </c>
       <c r="B31" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>135337857</v>
       </c>
       <c r="B32" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>135337862</v>
       </c>
       <c r="B33" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>135319835</v>
       </c>
       <c r="B34" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>135331126</v>
       </c>
       <c r="B35" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>135331128</v>
       </c>
       <c r="B36" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>135333186</v>
       </c>
       <c r="B37" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>135331143</v>
       </c>
       <c r="B38" t="n">
-        <v>83350</v>
+        <v>83390</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>135331036</v>
       </c>
       <c r="B39" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>135332782</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>135331144</v>
       </c>
       <c r="B41" t="n">
-        <v>83349</v>
+        <v>83389</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>135333369</v>
       </c>
       <c r="B42" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>135333379</v>
       </c>
       <c r="B43" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>135331034</v>
       </c>
       <c r="B44" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>135331031</v>
       </c>
       <c r="B45" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>135337861</v>
       </c>
       <c r="B46" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>135331028</v>
       </c>
       <c r="B47" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>135331037</v>
       </c>
       <c r="B48" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>135332774</v>
       </c>
       <c r="B49" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>135333363</v>
       </c>
       <c r="B50" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>135333367</v>
       </c>
       <c r="B51" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>135333370</v>
       </c>
       <c r="B52" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>135333377</v>
       </c>
       <c r="B53" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>135331123</v>
       </c>
       <c r="B54" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>135332769</v>
       </c>
       <c r="B55" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>135331027</v>
       </c>
       <c r="B56" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>135331029</v>
       </c>
       <c r="B57" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>135331350</v>
       </c>
       <c r="B58" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>135331670</v>
       </c>
       <c r="B59" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>135331033</v>
       </c>
       <c r="B60" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>135333364</v>
       </c>
       <c r="B61" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>135333375</v>
       </c>
       <c r="B62" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>135358216</v>
       </c>
       <c r="B63" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>135332772</v>
       </c>
       <c r="B64" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>135332775</v>
       </c>
       <c r="B65" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>135331035</v>
       </c>
       <c r="B66" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>135332771</v>
       </c>
       <c r="B67" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>135332776</v>
       </c>
       <c r="B68" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>135333181</v>
       </c>
       <c r="B69" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>135333371</v>
       </c>
       <c r="B70" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>135333374</v>
       </c>
       <c r="B71" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>135318090</v>
       </c>
       <c r="B72" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>135331038</v>
       </c>
       <c r="B73" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>135332777</v>
       </c>
       <c r="B74" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>135332781</v>
       </c>
       <c r="B75" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>135332783</v>
       </c>
       <c r="B76" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>135332786</v>
       </c>
       <c r="B77" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>135333182</v>
       </c>
       <c r="B78" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>135337852</v>
       </c>
       <c r="B79" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>135331121</v>
       </c>
       <c r="B80" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>135331122</v>
       </c>
       <c r="B81" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         <v>135332770</v>
       </c>
       <c r="B84" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>135333365</v>
       </c>
       <c r="B85" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>135333378</v>
       </c>
       <c r="B86" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>135333372</v>
       </c>
       <c r="B88" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>135331671</v>
       </c>
       <c r="B89" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>135331145</v>
       </c>
       <c r="B90" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>135331672</v>
       </c>
       <c r="B91" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>135331673</v>
       </c>
       <c r="B92" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>135331674</v>
       </c>
       <c r="B93" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>135331039</v>
       </c>
       <c r="B94" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>135331124</v>
       </c>
       <c r="B95" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>135331125</v>
       </c>
       <c r="B96" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>135331119</v>
       </c>
       <c r="B97" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>135331669</v>
       </c>
       <c r="B98" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>135332778</v>
       </c>
       <c r="B99" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>135333180</v>
       </c>
       <c r="B100" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>135333382</v>
       </c>
       <c r="B101" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135331137</v>
       </c>
       <c r="B2" t="n">
-        <v>83383</v>
+        <v>83410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>135331133</v>
       </c>
       <c r="B3" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>135331136</v>
       </c>
       <c r="B4" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>135333192</v>
       </c>
       <c r="B5" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>135333193</v>
       </c>
       <c r="B6" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>135337856</v>
       </c>
       <c r="B7" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>135333195</v>
       </c>
       <c r="B8" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>135331141</v>
       </c>
       <c r="B9" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>135331135</v>
       </c>
       <c r="B10" t="n">
-        <v>92209</v>
+        <v>92236</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>135331140</v>
       </c>
       <c r="B11" t="n">
-        <v>92209</v>
+        <v>92236</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>135331131</v>
       </c>
       <c r="B12" t="n">
-        <v>96722</v>
+        <v>96749</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>135331132</v>
       </c>
       <c r="B13" t="n">
-        <v>97352</v>
+        <v>97379</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>135320627</v>
       </c>
       <c r="B14" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>135319473</v>
       </c>
       <c r="B15" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>135319562</v>
       </c>
       <c r="B16" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>623499</v>
       </c>
       <c r="R16" t="n">
-        <v>7307488</v>
+        <v>7307487</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2423,7 +2423,7 @@
         <v>135331130</v>
       </c>
       <c r="B17" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>135333184</v>
       </c>
       <c r="B18" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>135333188</v>
       </c>
       <c r="B19" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>135333190</v>
       </c>
       <c r="B20" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>135320009</v>
       </c>
       <c r="B21" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>135333183</v>
       </c>
       <c r="B22" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>135319971</v>
       </c>
       <c r="B23" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>135333185</v>
       </c>
       <c r="B24" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>135333191</v>
       </c>
       <c r="B25" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>135337862</v>
       </c>
       <c r="B33" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>135319835</v>
       </c>
       <c r="B34" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>135331126</v>
       </c>
       <c r="B35" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>135331128</v>
       </c>
       <c r="B36" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>135333186</v>
       </c>
       <c r="B37" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>135331143</v>
       </c>
       <c r="B38" t="n">
-        <v>83390</v>
+        <v>83417</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>135331036</v>
       </c>
       <c r="B39" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>135332782</v>
       </c>
       <c r="B40" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>135331144</v>
       </c>
       <c r="B41" t="n">
-        <v>83389</v>
+        <v>83416</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>135333369</v>
       </c>
       <c r="B42" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>135333379</v>
       </c>
       <c r="B43" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>135331034</v>
       </c>
       <c r="B44" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>135331031</v>
       </c>
       <c r="B45" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>135337861</v>
       </c>
       <c r="B46" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>135331028</v>
       </c>
       <c r="B47" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>135331037</v>
       </c>
       <c r="B48" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>135332774</v>
       </c>
       <c r="B49" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>135333363</v>
       </c>
       <c r="B50" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>135333367</v>
       </c>
       <c r="B51" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>135333370</v>
       </c>
       <c r="B52" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>135333377</v>
       </c>
       <c r="B53" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>135331123</v>
       </c>
       <c r="B54" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>135332769</v>
       </c>
       <c r="B55" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>135331027</v>
       </c>
       <c r="B56" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>135331029</v>
       </c>
       <c r="B57" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>135331350</v>
       </c>
       <c r="B58" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>135331670</v>
       </c>
       <c r="B59" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>135331033</v>
       </c>
       <c r="B60" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>135333364</v>
       </c>
       <c r="B61" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>135333375</v>
       </c>
       <c r="B62" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>135358216</v>
       </c>
       <c r="B63" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>135332772</v>
       </c>
       <c r="B64" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>135332775</v>
       </c>
       <c r="B65" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>135331035</v>
       </c>
       <c r="B66" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>135332771</v>
       </c>
       <c r="B67" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8271,7 +8271,7 @@
         <v>135332776</v>
       </c>
       <c r="B68" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>135333181</v>
       </c>
       <c r="B69" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>135333372</v>
       </c>
       <c r="B88" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>135331671</v>
       </c>
       <c r="B89" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>135331145</v>
       </c>
       <c r="B90" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>135331672</v>
       </c>
       <c r="B91" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>135331673</v>
       </c>
       <c r="B92" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>135331674</v>
       </c>
       <c r="B93" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>135331039</v>
       </c>
       <c r="B94" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>135331124</v>
       </c>
       <c r="B95" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>135331125</v>
       </c>
       <c r="B96" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>135331119</v>
       </c>
       <c r="B97" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>135331669</v>
       </c>
       <c r="B98" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>135332778</v>
       </c>
       <c r="B99" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>135333180</v>
       </c>
       <c r="B100" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>135333382</v>
       </c>
       <c r="B101" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
+++ b/artfynd/Maskaure Tsågávrrie avvanm, 17,8 ha artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>135331133</v>
       </c>
       <c r="B3" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>135331136</v>
       </c>
       <c r="B4" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>135333192</v>
       </c>
       <c r="B5" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>135333193</v>
       </c>
       <c r="B6" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>135337856</v>
       </c>
       <c r="B7" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>135333195</v>
       </c>
       <c r="B8" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>135331135</v>
       </c>
       <c r="B10" t="n">
-        <v>92241</v>
+        <v>92243</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>135331140</v>
       </c>
       <c r="B11" t="n">
-        <v>92241</v>
+        <v>92243</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>135331131</v>
       </c>
       <c r="B12" t="n">
-        <v>96754</v>
+        <v>96756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>135331132</v>
       </c>
       <c r="B13" t="n">
-        <v>97384</v>
+        <v>97386</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>135320627</v>
       </c>
       <c r="B14" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>623499</v>
       </c>
       <c r="R16" t="n">
-        <v>7307488</v>
+        <v>7307487</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -4298,7 +4298,7 @@
         <v>135337862</v>
       </c>
       <c r="B33" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>135319835</v>
       </c>
       <c r="B34" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>135333379</v>
       </c>
       <c r="B43" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>135331031</v>
       </c>
       <c r="B45" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>135337861</v>
       </c>
       <c r="B46" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>135331123</v>
       </c>
       <c r="B54" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>135332769</v>
       </c>
       <c r="B55" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>135333372</v>
       </c>
       <c r="B88" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>135331671</v>
       </c>
       <c r="B89" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>135331145</v>
       </c>
       <c r="B90" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>135331672</v>
       </c>
       <c r="B91" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>135331673</v>
       </c>
       <c r="B92" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>135331674</v>
       </c>
       <c r="B93" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
